--- a/data/exports/football-recommendations-2026-05-23.xlsx
+++ b/data/exports/football-recommendations-2026-05-23.xlsx
@@ -257,17 +257,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>胜 2.35，平 3.15，负 3.2</t>
+          <t>胜 2.47，平 3.05，负 3.1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>盘口 -0.25，主水 1.05，客水 0.82</t>
+          <t>盘口 0，主水 0.76，客水 1.12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>胜 4.95，平 3.65，负 1.53</t>
+          <t>胜 5.2，平 3.7，负 1.5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -282,17 +282,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -317,11 +317,11 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="U2">
-        <v>31.25</v>
+        <v>25.43</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -336,7 +336,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>经模型综合分析：澳超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：澳超，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>客胜/主胜</t>
+          <t>主胜/平局</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3856,11 +3856,11 @@
         </is>
       </c>
       <c r="G3">
-        <v>48.48</v>
+        <v>92.23</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>概率差 25%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：德国杯，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>概率差 54%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：德国杯，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六014 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -3875,12 +3875,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>客胜/主胜</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3894,11 +3894,11 @@
         </is>
       </c>
       <c r="G4">
-        <v>72</v>
+        <v>42.08</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>概率差 41%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>概率差 19%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六013 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -3932,11 +3932,11 @@
         </is>
       </c>
       <c r="G5">
-        <v>46.37</v>
+        <v>69.75</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>概率差 23%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>概率差 37%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六016 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -3956,25 +3956,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>主胜/平局/客胜</t>
+          <t>主胜/平局</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>全选</t>
+          <t>双选</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G6">
-        <v>22.44</v>
+        <v>57.89</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>概率差 6%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>概率差 29%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六022 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -3994,25 +3994,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>主胜/平局/客胜</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>双选</t>
+          <t>全选</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G7">
-        <v>50.37</v>
+        <v>18.51</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>概率差 26%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>概率差 2%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六021 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>主胜/客胜</t>
+          <t>主胜/平局</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4046,11 +4046,11 @@
         </is>
       </c>
       <c r="G8">
-        <v>39.07</v>
+        <v>57.62</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>概率差 17%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>概率差 29%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六017 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -4070,25 +4070,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>主胜/平局/客胜</t>
+          <t>主胜/客胜</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>全选</t>
+          <t>双选</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G9">
-        <v>23.68</v>
+        <v>36.46</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>概率差 7%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：荷乙，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>概率差 13%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：荷乙，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六015 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -4160,11 +4160,11 @@
         </is>
       </c>
       <c r="G11">
-        <v>35.72</v>
+        <v>46.6</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>概率差 15%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>概率差 21%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六007 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>主胜/客胜</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4198,11 +4198,11 @@
         </is>
       </c>
       <c r="G12">
-        <v>52.93</v>
+        <v>51.41</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>概率差 28%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>概率差 25%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六008 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -4236,11 +4236,11 @@
         </is>
       </c>
       <c r="G13">
-        <v>46.24</v>
+        <v>46.73</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>概率差 23%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>概率差 21%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六011 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -4274,11 +4274,11 @@
         </is>
       </c>
       <c r="G14">
-        <v>61.61</v>
+        <v>67.88</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>概率差 33%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>概率差 36%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六010 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -4312,11 +4312,11 @@
         </is>
       </c>
       <c r="G15">
-        <v>15.65</v>
+        <v>19.36</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>概率差 1%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>概率差 1%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六009 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-23T07:15:44.792Z</t>
+          <t>2026-05-23T07:20:31.388Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="J2">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="K2">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L2">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="M2">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="N2">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O2">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -4700,22 +4700,22 @@
         </is>
       </c>
       <c r="S2">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>1.05</v>
+        <v>0.76</v>
       </c>
       <c r="U2">
-        <v>0.82</v>
+        <v>1.12</v>
       </c>
       <c r="V2">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>0.76</v>
       </c>
       <c r="X2">
-        <v>0.82</v>
+        <v>1.12</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -4742,27 +4742,27 @@
         <v>1.57</v>
       </c>
       <c r="AE2">
-        <v>4.95</v>
+        <v>5.2</v>
       </c>
       <c r="AF2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AG2">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>+0.38</t>
+          <t>+0.63</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.05</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -4812,15 +4812,15 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="AU2">
-        <v>31.25</v>
+        <v>25.43</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>经模型综合分析：澳超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：澳超，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:16.334Z</t>
+          <t>2026-05-23T07:21:01.921Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:16.335Z</t>
+          <t>2026-05-23T07:21:01.921Z</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:05.200Z</t>
+          <t>2026-05-23T07:20:50.927Z</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -5282,10 +5282,10 @@
         <v>1.488</v>
       </c>
       <c r="K5">
-        <v>4.126</v>
+        <v>4.137</v>
       </c>
       <c r="L5">
-        <v>5.952</v>
+        <v>5.925</v>
       </c>
       <c r="M5">
         <v>1.438</v>
@@ -5303,22 +5303,22 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>+0.151</t>
+          <t>+0.14</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>+0.503</t>
+          <t>+0.53</t>
         </is>
       </c>
       <c r="S5">
         <v>-1.487</v>
       </c>
       <c r="T5">
-        <v>0.964</v>
+        <v>0.962</v>
       </c>
       <c r="U5">
-        <v>1.657</v>
+        <v>1.658</v>
       </c>
       <c r="V5">
         <v>-1.642</v>
@@ -5336,12 +5336,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>+0.018</t>
+          <t>+0.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>+0.355</t>
+          <t>+0.354</t>
         </is>
       </c>
       <c r="AB5">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:16.368Z</t>
+          <t>2026-05-23T07:21:01.928Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:16.366Z</t>
+          <t>2026-05-23T07:21:01.928Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:06.275Z</t>
+          <t>2026-05-23T07:20:51.987Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="J8">
-        <v>2.03</v>
+        <v>2.029</v>
       </c>
       <c r="K8">
         <v>3.577</v>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-0.161</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:07.330Z</t>
+          <t>2026-05-23T07:20:53.041Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -6101,7 +6101,7 @@
         <v>3.458</v>
       </c>
       <c r="L9">
-        <v>2.489</v>
+        <v>2.488</v>
       </c>
       <c r="M9">
         <v>2.472</v>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>+0.078</t>
+          <t>+0.079</t>
         </is>
       </c>
       <c r="S9">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-05-23T07:15:40.705Z</t>
+          <t>2026-05-23T07:20:27.901Z</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-05-23T07:15:40.705Z</t>
+          <t>2026-05-23T07:20:27.901Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:16.381Z</t>
+          <t>2026-05-23T07:21:01.929Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:17.673Z</t>
+          <t>2026-05-23T07:21:03.209Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-05-23T07:15:40.705Z</t>
+          <t>2026-05-23T07:20:27.901Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:17.675Z</t>
+          <t>2026-05-23T07:21:03.209Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:17.688Z</t>
+          <t>2026-05-23T07:21:03.211Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:17.742Z</t>
+          <t>2026-05-23T07:21:03.216Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:08.391Z</t>
+          <t>2026-05-23T07:20:54.091Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="J18">
-        <v>1.445</v>
+        <v>1.446</v>
       </c>
       <c r="K18">
-        <v>4.399</v>
+        <v>4.398</v>
       </c>
       <c r="L18">
-        <v>6.965</v>
+        <v>6.96</v>
       </c>
       <c r="M18">
         <v>1.466</v>
@@ -7950,17 +7950,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>+0.021</t>
+          <t>+0.02</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>-0.186</t>
+          <t>-0.185</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>-0.546</t>
+          <t>-0.541</t>
         </is>
       </c>
       <c r="S18">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:17.712Z</t>
+          <t>2026-05-23T07:21:03.213Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:09.457Z</t>
+          <t>2026-05-23T07:20:55.141Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8339,13 +8339,13 @@
         </is>
       </c>
       <c r="J20">
-        <v>1.444</v>
+        <v>1.447</v>
       </c>
       <c r="K20">
-        <v>4.727</v>
+        <v>4.709</v>
       </c>
       <c r="L20">
-        <v>6.033</v>
+        <v>6.01</v>
       </c>
       <c r="M20">
         <v>1.435</v>
@@ -8358,17 +8358,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>-0.009</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-0.071</t>
+          <t>-0.053</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>-0.055</t>
+          <t>-0.032</t>
         </is>
       </c>
       <c r="S20">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:17.738Z</t>
+          <t>2026-05-23T07:21:03.215Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-05-23T07:15:40.706Z</t>
+          <t>2026-05-23T07:20:27.901Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:17.726Z</t>
+          <t>2026-05-23T07:21:03.214Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:10.518Z</t>
+          <t>2026-05-23T07:20:56.193Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -9155,10 +9155,10 @@
         </is>
       </c>
       <c r="J24">
-        <v>3.396</v>
+        <v>3.4</v>
       </c>
       <c r="K24">
-        <v>3.961</v>
+        <v>3.963</v>
       </c>
       <c r="L24">
         <v>1.932</v>
@@ -9174,12 +9174,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>+0.116</t>
+          <t>+0.112</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.024</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -9194,7 +9194,7 @@
         <v>1.315</v>
       </c>
       <c r="U24">
-        <v>1.098</v>
+        <v>1.099</v>
       </c>
       <c r="V24">
         <v>-0.181</v>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-0.063</t>
+          <t>-0.064</t>
         </is>
       </c>
       <c r="AB24">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-05-23T07:15:40.706Z</t>
+          <t>2026-05-23T07:20:27.901Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:11.582Z</t>
+          <t>2026-05-23T07:20:57.250Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:12.647Z</t>
+          <t>2026-05-23T07:20:58.298Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:13.710Z</t>
+          <t>2026-05-23T07:20:59.361Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -9974,10 +9974,10 @@
         <v>2.01</v>
       </c>
       <c r="K28">
-        <v>3.57</v>
+        <v>3.569</v>
       </c>
       <c r="L28">
-        <v>3.307</v>
+        <v>3.306</v>
       </c>
       <c r="M28">
         <v>1.897</v>
@@ -9995,12 +9995,12 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.021</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>+0.285</t>
+          <t>+0.286</t>
         </is>
       </c>
       <c r="S28">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:18.264Z</t>
+          <t>2026-05-23T07:21:03.705Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:14.767Z</t>
+          <t>2026-05-23T07:21:00.405Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:16.387Z</t>
+          <t>2026-05-23T07:21:01.929Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -10790,7 +10790,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-05-23T07:13:13.000Z</t>
+          <t>2026-05-23T07:19:43.000Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -10926,32 +10926,32 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>平局-客胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-平局</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
@@ -10960,11 +10960,11 @@
         </is>
       </c>
       <c r="AU32">
-        <v>48.48</v>
+        <v>92.23</v>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>经模型综合分析：德国杯，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：德国杯，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六014 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-05-23T07:13:19.000Z</t>
+          <t>2026-05-23T07:19:52.000Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -11015,13 +11015,13 @@
         </is>
       </c>
       <c r="J33">
-        <v>1.698</v>
+        <v>1.697</v>
       </c>
       <c r="K33">
-        <v>3.889</v>
+        <v>3.892</v>
       </c>
       <c r="L33">
-        <v>4.75</v>
+        <v>4.753</v>
       </c>
       <c r="M33">
         <v>1.491</v>
@@ -11034,17 +11034,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>-0.207</t>
+          <t>-0.206</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>+0.366</t>
+          <t>+0.363</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>+1.351</t>
+          <t>+1.348</t>
         </is>
       </c>
       <c r="S33">
@@ -11063,7 +11063,7 @@
         <v>1.881</v>
       </c>
       <c r="X33">
-        <v>1.904</v>
+        <v>1.906</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>-0.028</t>
+          <t>-0.026</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -11142,32 +11142,32 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>平局</t>
-        </is>
-      </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>主胜-客胜</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>客胜-主胜</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
@@ -11176,11 +11176,11 @@
         </is>
       </c>
       <c r="AU33">
-        <v>72</v>
+        <v>42.08</v>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六013 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-05-23T07:13:20.000Z</t>
+          <t>2026-05-23T07:19:53.000Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -11231,13 +11231,13 @@
         </is>
       </c>
       <c r="J34">
-        <v>1.809</v>
+        <v>1.811</v>
       </c>
       <c r="K34">
-        <v>3.584</v>
+        <v>3.581</v>
       </c>
       <c r="L34">
-        <v>4.444</v>
+        <v>4.435</v>
       </c>
       <c r="M34">
         <v>1.89</v>
@@ -11250,17 +11250,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>+0.081</t>
+          <t>+0.079</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>-0.074</t>
+          <t>-0.071</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>-0.532</t>
+          <t>-0.523</t>
         </is>
       </c>
       <c r="S34">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -11392,11 +11392,11 @@
         </is>
       </c>
       <c r="AU34">
-        <v>46.37</v>
+        <v>69.75</v>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六016 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-05-23T07:16:17.708Z</t>
+          <t>2026-05-23T07:21:03.212Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
@@ -11604,15 +11604,15 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="AU35">
-        <v>22.44</v>
+        <v>57.89</v>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六022 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-05-23T07:13:20.000Z</t>
+          <t>2026-05-23T07:19:52.000Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
@@ -11820,15 +11820,15 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="AU36">
-        <v>50.37</v>
+        <v>18.51</v>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六021 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -11870,7 +11870,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-05-23T07:13:20.000Z</t>
+          <t>2026-05-23T07:16:37.000Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>平局-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
@@ -12040,11 +12040,11 @@
         </is>
       </c>
       <c r="AU37">
-        <v>39.07</v>
+        <v>57.62</v>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六017 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-05-23T07:13:03.000Z</t>
+          <t>2026-05-23T07:19:34.000Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -12095,13 +12095,13 @@
         </is>
       </c>
       <c r="J38">
-        <v>2.169</v>
+        <v>2.172</v>
       </c>
       <c r="K38">
         <v>3.51</v>
       </c>
       <c r="L38">
-        <v>3.036</v>
+        <v>3.03</v>
       </c>
       <c r="M38">
         <v>2.303</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>+0.134</t>
+          <t>+0.131</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>-0.232</t>
+          <t>-0.226</t>
         </is>
       </c>
       <c r="S38">
@@ -12140,10 +12140,10 @@
         <v>-0.281</v>
       </c>
       <c r="W38">
-        <v>1.951</v>
+        <v>1.956</v>
       </c>
       <c r="X38">
-        <v>1.868</v>
+        <v>1.865</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -12152,12 +12152,12 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>+0.15</t>
+          <t>+0.155</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>-0.076</t>
+          <t>-0.079</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -12252,15 +12252,15 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="AU38">
-        <v>23.68</v>
+        <v>36.46</v>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六015 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -12302,7 +12302,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-05-23T07:12:48.000Z</t>
+          <t>2026-05-23T07:19:19.000Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-05-23T07:12:48.000Z</t>
+          <t>2026-05-23T07:19:19.000Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -12572,10 +12572,10 @@
         <v>-0.5</v>
       </c>
       <c r="W40">
-        <v>1.878</v>
+        <v>1.887</v>
       </c>
       <c r="X40">
-        <v>1.928</v>
+        <v>1.92</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -12584,12 +12584,12 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>-0.058</t>
+          <t>-0.049</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>+0.056</t>
+          <t>+0.048</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -12688,11 +12688,11 @@
         </is>
       </c>
       <c r="AU40">
-        <v>35.72</v>
+        <v>46.6</v>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六007 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -12734,7 +12734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-05-23T07:12:55.000Z</t>
+          <t>2026-05-23T07:19:27.000Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -12785,27 +12785,27 @@
         <v>1.923</v>
       </c>
       <c r="V41">
-        <v>-0.433</v>
+        <v>-0.417</v>
       </c>
       <c r="W41">
-        <v>1.953</v>
+        <v>1.937</v>
       </c>
       <c r="X41">
-        <v>1.867</v>
+        <v>1.883</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>+0.15</t>
+          <t>+0.166</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>+0.068</t>
+          <t>+0.052</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>-0.056</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>主胜-客胜</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr">
@@ -12904,11 +12904,11 @@
         </is>
       </c>
       <c r="AU41">
-        <v>52.93</v>
+        <v>51.41</v>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六008 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-05-23T07:12:55.000Z</t>
+          <t>2026-05-23T07:19:27.000Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -12959,13 +12959,13 @@
         </is>
       </c>
       <c r="J42">
-        <v>1.859</v>
+        <v>1.858</v>
       </c>
       <c r="K42">
         <v>3.453</v>
       </c>
       <c r="L42">
-        <v>3.947</v>
+        <v>3.953</v>
       </c>
       <c r="M42">
         <v>1.866</v>
@@ -12978,7 +12978,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>+0.007</t>
+          <t>+0.008</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>-0.184</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="S42">
@@ -13004,10 +13004,10 @@
         <v>-0.517</v>
       </c>
       <c r="W42">
-        <v>1.874</v>
+        <v>1.876</v>
       </c>
       <c r="X42">
-        <v>1.938</v>
+        <v>1.935</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -13016,12 +13016,12 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>-0.073</t>
+          <t>-0.071</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>+0.089</t>
+          <t>+0.086</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -13120,11 +13120,11 @@
         </is>
       </c>
       <c r="AU42">
-        <v>46.24</v>
+        <v>46.73</v>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六011 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -13166,7 +13166,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-05-23T07:12:55.000Z</t>
+          <t>2026-05-23T07:19:28.000Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -13175,7 +13175,7 @@
         </is>
       </c>
       <c r="J43">
-        <v>1.591</v>
+        <v>1.592</v>
       </c>
       <c r="K43">
         <v>3.825</v>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.001</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -13217,27 +13217,27 @@
         <v>1.826</v>
       </c>
       <c r="V43">
-        <v>-0.781</v>
+        <v>-0.797</v>
       </c>
       <c r="W43">
-        <v>1.831</v>
+        <v>1.852</v>
       </c>
       <c r="X43">
-        <v>1.932</v>
+        <v>1.914</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>+0.094</t>
+          <t>+0.078</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>-0.077</t>
+          <t>-0.056</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>+0.106</t>
+          <t>+0.088</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
@@ -13336,11 +13336,11 @@
         </is>
       </c>
       <c r="AU43">
-        <v>61.61</v>
+        <v>67.88</v>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六010 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-05-23T07:12:56.000Z</t>
+          <t>2026-05-23T07:19:28.000Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -13436,10 +13436,10 @@
         <v>0.031</v>
       </c>
       <c r="W44">
-        <v>1.912</v>
+        <v>1.913</v>
       </c>
       <c r="X44">
-        <v>1.846</v>
+        <v>1.845</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -13448,12 +13448,12 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>+0.067</t>
+          <t>+0.068</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.002</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -13552,11 +13552,11 @@
         </is>
       </c>
       <c r="AU44">
-        <v>15.65</v>
+        <v>19.36</v>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六009 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -13857,21 +13857,21 @@
         </is>
       </c>
       <c r="R2">
-        <v>2.648</v>
+        <v>2.62</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>经模型综合分析：澳超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：澳超，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
     </row>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>经模型综合分析：德国杯，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：德国杯，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六014 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六013 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -19211,7 +19211,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六016 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -19376,7 +19376,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六022 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -19541,7 +19541,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六021 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六017 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -19871,7 +19871,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六015 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六007 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -20366,7 +20366,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六008 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六011 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -20696,7 +20696,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六010 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -20861,7 +20861,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六009 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -21103,44 +21103,44 @@
         </is>
       </c>
       <c r="K2">
-        <v>0.4032</v>
+        <v>0.3836</v>
       </c>
       <c r="L2">
-        <v>0.3008</v>
+        <v>0.3107</v>
       </c>
       <c r="M2">
-        <v>0.2961</v>
+        <v>0.3057</v>
       </c>
       <c r="N2">
-        <v>0.4032</v>
+        <v>0.3836</v>
       </c>
       <c r="O2">
-        <v>0.3008</v>
+        <v>0.3107</v>
       </c>
       <c r="P2">
-        <v>0.2961</v>
+        <v>0.3057</v>
       </c>
       <c r="Q2">
-        <v>0.4666</v>
+        <v>0.4418</v>
       </c>
       <c r="R2">
-        <v>0.2588</v>
+        <v>0.2611</v>
       </c>
       <c r="S2">
-        <v>0.2747</v>
+        <v>0.2972</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1-1:12.3% / 1-0:10.6% / 2-1:9.2%</t>
+          <t>1-1:12.5% / 1-0:10.7% / 2-1:9%</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V2">
-        <v>31.25</v>
+        <v>25.43</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>经模型综合分析：澳超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：澳超，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -24764,42 +24764,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>平局-客胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-平局</t>
         </is>
       </c>
       <c r="K32">
-        <v>0.2543</v>
+        <v>0.7045</v>
       </c>
       <c r="L32">
-        <v>0.2447</v>
+        <v>0.1655</v>
       </c>
       <c r="M32">
-        <v>0.501</v>
+        <v>0.13</v>
       </c>
       <c r="N32">
         <v>0.2543</v>
@@ -24830,7 +24830,7 @@
         </is>
       </c>
       <c r="V32">
-        <v>48.48</v>
+        <v>92.23</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>经模型综合分析：德国杯，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：德国杯，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六014 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -24887,42 +24887,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>平局</t>
-        </is>
-      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>主胜-客胜</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>客胜-主胜</t>
         </is>
       </c>
       <c r="K33">
-        <v>0.627</v>
+        <v>0.2785</v>
       </c>
       <c r="L33">
-        <v>0.2197</v>
+        <v>0.253</v>
       </c>
       <c r="M33">
-        <v>0.1532</v>
+        <v>0.4685</v>
       </c>
       <c r="N33">
         <v>0.627</v>
@@ -24953,7 +24953,7 @@
         </is>
       </c>
       <c r="V33">
-        <v>72</v>
+        <v>42.08</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六013 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -25020,7 +25020,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -25039,13 +25039,13 @@
         </is>
       </c>
       <c r="K34">
-        <v>0.4947</v>
+        <v>0.6014</v>
       </c>
       <c r="L34">
-        <v>0.2664</v>
+        <v>0.2297</v>
       </c>
       <c r="M34">
-        <v>0.239</v>
+        <v>0.1689</v>
       </c>
       <c r="N34">
         <v>0.4947</v>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="V34">
-        <v>46.37</v>
+        <v>69.75</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六016 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -25148,7 +25148,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -25162,13 +25162,13 @@
         </is>
       </c>
       <c r="K35">
-        <v>0.3949</v>
+        <v>0.5438</v>
       </c>
       <c r="L35">
-        <v>0.3331</v>
+        <v>0.2578</v>
       </c>
       <c r="M35">
-        <v>0.272</v>
+        <v>0.1984</v>
       </c>
       <c r="N35">
         <v>0.3949</v>
@@ -25195,11 +25195,11 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="V35">
-        <v>22.44</v>
+        <v>57.89</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六022 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -25271,7 +25271,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -25285,13 +25285,13 @@
         </is>
       </c>
       <c r="K36">
-        <v>0.5101</v>
+        <v>0.3719</v>
       </c>
       <c r="L36">
-        <v>0.2496</v>
+        <v>0.3471</v>
       </c>
       <c r="M36">
-        <v>0.2402</v>
+        <v>0.281</v>
       </c>
       <c r="N36">
         <v>0.5101</v>
@@ -25318,11 +25318,11 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V36">
-        <v>50.37</v>
+        <v>18.51</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六021 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -25384,7 +25384,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -25394,7 +25394,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -25404,17 +25404,17 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>平局-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K37">
-        <v>0.4605</v>
+        <v>0.5348</v>
       </c>
       <c r="L37">
-        <v>0.2536</v>
+        <v>0.2446</v>
       </c>
       <c r="M37">
-        <v>0.2859</v>
+        <v>0.2206</v>
       </c>
       <c r="N37">
         <v>0.4605</v>
@@ -25445,7 +25445,7 @@
         </is>
       </c>
       <c r="V37">
-        <v>39.07</v>
+        <v>57.62</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六017 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -25531,13 +25531,13 @@
         </is>
       </c>
       <c r="K38">
-        <v>0.3999</v>
+        <v>0.4352</v>
       </c>
       <c r="L38">
-        <v>0.2717</v>
+        <v>0.2643</v>
       </c>
       <c r="M38">
-        <v>0.3284</v>
+        <v>0.3005</v>
       </c>
       <c r="N38">
         <v>0.3999</v>
@@ -25564,11 +25564,11 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="V38">
-        <v>23.68</v>
+        <v>36.46</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六015 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -25777,13 +25777,13 @@
         </is>
       </c>
       <c r="K40">
-        <v>0.443</v>
+        <v>0.4872</v>
       </c>
       <c r="L40">
-        <v>0.2916</v>
+        <v>0.2814</v>
       </c>
       <c r="M40">
-        <v>0.2655</v>
+        <v>0.2314</v>
       </c>
       <c r="N40">
         <v>0.443</v>
@@ -25814,7 +25814,7 @@
         </is>
       </c>
       <c r="V40">
-        <v>35.72</v>
+        <v>46.6</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六007 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -25876,7 +25876,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -25886,7 +25886,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -25896,17 +25896,17 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>主胜-客胜</t>
         </is>
       </c>
       <c r="K41">
-        <v>0.521</v>
+        <v>0.5009</v>
       </c>
       <c r="L41">
-        <v>0.2408</v>
+        <v>0.2465</v>
       </c>
       <c r="M41">
-        <v>0.2382</v>
+        <v>0.2526</v>
       </c>
       <c r="N41">
         <v>0.521</v>
@@ -25937,7 +25937,7 @@
         </is>
       </c>
       <c r="V41">
-        <v>52.93</v>
+        <v>51.41</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六008 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -26023,13 +26023,13 @@
         </is>
       </c>
       <c r="K42">
-        <v>0.4923</v>
+        <v>0.4828</v>
       </c>
       <c r="L42">
-        <v>0.2635</v>
+        <v>0.272</v>
       </c>
       <c r="M42">
-        <v>0.2441</v>
+        <v>0.2452</v>
       </c>
       <c r="N42">
         <v>0.4923</v>
@@ -26060,7 +26060,7 @@
         </is>
       </c>
       <c r="V42">
-        <v>46.24</v>
+        <v>46.73</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -26075,7 +26075,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六011 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -26127,7 +26127,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -26146,13 +26146,13 @@
         </is>
       </c>
       <c r="K43">
-        <v>0.5759</v>
+        <v>0.5934</v>
       </c>
       <c r="L43">
-        <v>0.2432</v>
+        <v>0.2361</v>
       </c>
       <c r="M43">
-        <v>0.181</v>
+        <v>0.1705</v>
       </c>
       <c r="N43">
         <v>0.5759</v>
@@ -26183,7 +26183,7 @@
         </is>
       </c>
       <c r="V43">
-        <v>61.61</v>
+        <v>67.88</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六010 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -26269,13 +26269,13 @@
         </is>
       </c>
       <c r="K44">
-        <v>0.369</v>
+        <v>0.3731</v>
       </c>
       <c r="L44">
-        <v>0.2689</v>
+        <v>0.2676</v>
       </c>
       <c r="M44">
-        <v>0.362</v>
+        <v>0.3593</v>
       </c>
       <c r="N44">
         <v>0.369</v>
@@ -26306,7 +26306,7 @@
         </is>
       </c>
       <c r="V44">
-        <v>15.65</v>
+        <v>19.36</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六009 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">

--- a/data/exports/football-recommendations-2026-05-23.xlsx
+++ b/data/exports/football-recommendations-2026-05-23.xlsx
@@ -257,7 +257,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>胜 1.99，平 3.1，负 3.3</t>
+          <t>胜 1.95，平 3.1，负 3.4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -267,7 +267,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>胜 4.15，平 3.6，负 1.64</t>
+          <t>胜 4.1，平 3.55，负 1.66</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -282,7 +282,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -292,7 +292,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -321,7 +321,7 @@
         </is>
       </c>
       <c r="U2">
-        <v>37.67</v>
+        <v>39.09</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -329,7 +329,7 @@
         </is>
       </c>
       <c r="W2">
-        <v>-0.1137</v>
+        <v>-0.1147</v>
       </c>
       <c r="X2">
         <v>0</v>
@@ -388,7 +388,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>胜 3.63，平 3.28，负 1.82</t>
+          <t>胜 3.8，平 3.28，负 1.78</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>胜 3.42，平 3.35，负 1.86</t>
+          <t>胜 3.5，平 3.4，负 1.82</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>胜 1.78，平 3.42，负 3.65</t>
+          <t>胜 1.75，平 3.42，负 3.76</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>胜 1.77，平 4.1，负 3.12</t>
+          <t>胜 1.74，平 4.25，负 3.13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>胜 2.2，平 3.3，负 2.7</t>
+          <t>胜 2.18，平 3.25，负 2.76</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>胜 3.28，平 3.35，负 1.9</t>
+          <t>胜 3.45，平 3.35，负 1.85</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>胜 2.26，平 2.9，负 2.92</t>
+          <t>胜 2.26，平 2.85，负 2.98</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2344,12 +2344,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="U19">
-        <v>27.24</v>
+        <v>26.77</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="W19">
-        <v>-0.1148</v>
+        <v>-0.1143</v>
       </c>
       <c r="X19">
         <v>0</v>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>胜 3.46，平 3.55，负 1.79</t>
+          <t>胜 3.58，平 3.55，负 1.76</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:14.309Z</t>
+          <t>2026-05-23T12:38:25.061Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -4192,17 +4192,17 @@
         <v>3.45</v>
       </c>
       <c r="M2">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="N2">
         <v>3.1</v>
       </c>
       <c r="O2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>+0.12</t>
+          <t>+0.08</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="S2">
@@ -4258,27 +4258,27 @@
         <v>1.7</v>
       </c>
       <c r="AE2">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AF2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AG2">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>+0.3</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>+0.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="AU2">
-        <v>37.67</v>
+        <v>39.09</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:14.309Z</t>
+          <t>2026-05-23T12:38:25.061Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -4462,27 +4462,27 @@
         <v>1.79</v>
       </c>
       <c r="AE3">
-        <v>3.63</v>
+        <v>3.8</v>
       </c>
       <c r="AF3">
         <v>3.28</v>
       </c>
       <c r="AG3">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
+          <t>+0.1</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>+0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:04.194Z</t>
+          <t>2026-05-23T12:38:15.009Z</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -4591,13 +4591,13 @@
         </is>
       </c>
       <c r="J4">
-        <v>2.072</v>
+        <v>2.074</v>
       </c>
       <c r="K4">
-        <v>3.582</v>
+        <v>3.581</v>
       </c>
       <c r="L4">
-        <v>3.201</v>
+        <v>3.211</v>
       </c>
       <c r="M4">
         <v>1.869</v>
@@ -4610,27 +4610,27 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-0.203</t>
+          <t>-0.205</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>+0.216</t>
+          <t>+0.217</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>+0.506</t>
+          <t>+0.496</t>
         </is>
       </c>
       <c r="S4">
-        <v>-1.062</v>
+        <v>-1.042</v>
       </c>
       <c r="T4">
-        <v>1.127</v>
+        <v>1.104</v>
       </c>
       <c r="U4">
-        <v>1.495</v>
+        <v>1.518</v>
       </c>
       <c r="V4">
         <v>-1.338</v>
@@ -4643,17 +4643,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-0.276</t>
+          <t>-0.296</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.015</t>
+          <t>+0.008</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>+0.081</t>
+          <t>+0.058</t>
         </is>
       </c>
       <c r="AB4">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:05.265Z</t>
+          <t>2026-05-23T12:38:16.065Z</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -4795,13 +4795,13 @@
         </is>
       </c>
       <c r="J5">
-        <v>2.498</v>
+        <v>2.454</v>
       </c>
       <c r="K5">
-        <v>3.434</v>
+        <v>3.431</v>
       </c>
       <c r="L5">
-        <v>2.581</v>
+        <v>2.636</v>
       </c>
       <c r="M5">
         <v>2.472</v>
@@ -4814,27 +4814,27 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-0.026</t>
+          <t>+0.018</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>+0.012</t>
+          <t>+0.015</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-0.014</t>
+          <t>-0.069</t>
         </is>
       </c>
       <c r="S5">
         <v>-0.523</v>
       </c>
       <c r="T5">
-        <v>1.122</v>
+        <v>1.094</v>
       </c>
       <c r="U5">
-        <v>1.192</v>
+        <v>1.221</v>
       </c>
       <c r="V5">
         <v>-0.554</v>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>+0.026</t>
+          <t>+0.054</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.037</t>
+          <t>-0.066</t>
         </is>
       </c>
       <c r="AB5">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-23T11:54:43.639Z</t>
+          <t>2026-05-23T12:37:54.468Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-05-23T11:54:43.639Z</t>
+          <t>2026-05-23T12:37:54.468Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -5278,27 +5278,27 @@
         <v>2</v>
       </c>
       <c r="AE7">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AF7">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AG7">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>+0.32</t>
+          <t>+0.4</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>+0.08</t>
+          <t>+0.13</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:14.311Z</t>
+          <t>2026-05-23T12:38:25.062Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -5482,17 +5482,17 @@
         <v>3.05</v>
       </c>
       <c r="AE8">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AF8">
         <v>3.42</v>
       </c>
       <c r="AG8">
-        <v>3.65</v>
+        <v>3.76</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>+0.6</t>
+          <t>+0.71</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:15.522Z</t>
+          <t>2026-05-23T12:38:26.266Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-05-23T11:54:43.639Z</t>
+          <t>2026-05-23T12:37:54.468Z</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -5890,27 +5890,27 @@
         <v>2.95</v>
       </c>
       <c r="AE10">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AF10">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="AG10">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>+0.17</t>
+          <t>+0.18</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:15.523Z</t>
+          <t>2026-05-23T12:38:26.266Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:15.524Z</t>
+          <t>2026-05-23T12:38:26.267Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:15.528Z</t>
+          <t>2026-05-23T12:38:26.272Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:06.335Z</t>
+          <t>2026-05-23T12:38:17.123Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6631,13 +6631,13 @@
         </is>
       </c>
       <c r="J14">
-        <v>1.465</v>
+        <v>1.467</v>
       </c>
       <c r="K14">
-        <v>4.353</v>
+        <v>4.373</v>
       </c>
       <c r="L14">
-        <v>6.818</v>
+        <v>6.839</v>
       </c>
       <c r="M14">
         <v>1.466</v>
@@ -6650,27 +6650,27 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>+0.001</t>
+          <t>-0.001</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>-0.399</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="S14">
-        <v>-1.812</v>
+        <v>-1.792</v>
       </c>
       <c r="T14">
-        <v>0.99</v>
+        <v>0.969</v>
       </c>
       <c r="U14">
-        <v>2.232</v>
+        <v>2.252</v>
       </c>
       <c r="V14">
         <v>-1.769</v>
@@ -6683,17 +6683,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>+0.043</t>
+          <t>+0.023</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>+0.048</t>
+          <t>+0.069</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.066</t>
+          <t>-0.086</t>
         </is>
       </c>
       <c r="AB14">
@@ -6706,27 +6706,27 @@
         <v>2.7</v>
       </c>
       <c r="AE14">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AF14">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AG14">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.06</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:15.526Z</t>
+          <t>2026-05-23T12:38:26.269Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:07.407Z</t>
+          <t>2026-05-23T12:38:18.183Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7039,13 +7039,13 @@
         </is>
       </c>
       <c r="J16">
-        <v>1.467</v>
+        <v>1.478</v>
       </c>
       <c r="K16">
-        <v>4.727</v>
+        <v>4.695</v>
       </c>
       <c r="L16">
-        <v>5.915</v>
+        <v>5.778</v>
       </c>
       <c r="M16">
         <v>1.435</v>
@@ -7058,27 +7058,27 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>-0.032</t>
+          <t>-0.043</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-0.071</t>
+          <t>-0.039</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>+0.063</t>
+          <t>+0.2</t>
         </is>
       </c>
       <c r="S16">
-        <v>-1.754</v>
+        <v>-1.715</v>
       </c>
       <c r="T16">
-        <v>1.062</v>
+        <v>1.034</v>
       </c>
       <c r="U16">
-        <v>1.581</v>
+        <v>1.611</v>
       </c>
       <c r="V16">
         <v>-1.815</v>
@@ -7091,17 +7091,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>-0.061</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>+0.008</t>
+          <t>+0.036</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>+0.054</t>
+          <t>+0.024</t>
         </is>
       </c>
       <c r="AB16">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:15.528Z</t>
+          <t>2026-05-23T12:38:26.272Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-05-23T11:54:43.640Z</t>
+          <t>2026-05-23T12:37:54.469Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7522,17 +7522,17 @@
         <v>2.03</v>
       </c>
       <c r="AE18">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AF18">
         <v>3.35</v>
       </c>
       <c r="AG18">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>+0.28</t>
+          <t>+0.45</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:15.527Z</t>
+          <t>2026-05-23T12:38:26.270Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -7663,10 +7663,10 @@
         <v>2.26</v>
       </c>
       <c r="N19">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="O19">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -7675,12 +7675,12 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>+0.22</t>
+          <t>+0.28</t>
         </is>
       </c>
       <c r="S19">
@@ -7800,7 +7800,7 @@
         </is>
       </c>
       <c r="AU19">
-        <v>27.24</v>
+        <v>26.77</v>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:08.473Z</t>
+          <t>2026-05-23T12:38:19.244Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -7855,13 +7855,13 @@
         </is>
       </c>
       <c r="J20">
-        <v>3.248</v>
+        <v>3.251</v>
       </c>
       <c r="K20">
-        <v>3.942</v>
+        <v>3.955</v>
       </c>
       <c r="L20">
-        <v>1.995</v>
+        <v>1.998</v>
       </c>
       <c r="M20">
         <v>3.512</v>
@@ -7874,27 +7874,27 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>+0.264</t>
+          <t>+0.261</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-0.003</t>
+          <t>-0.016</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>-0.144</t>
+          <t>-0.147</t>
         </is>
       </c>
       <c r="S20">
         <v>-0.158</v>
       </c>
       <c r="T20">
-        <v>1.218</v>
+        <v>1.223</v>
       </c>
       <c r="U20">
-        <v>1.166</v>
+        <v>1.173</v>
       </c>
       <c r="V20">
         <v>-0.181</v>
@@ -7912,12 +7912,12 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>+0.181</t>
+          <t>+0.176</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.131</t>
+          <t>-0.138</t>
         </is>
       </c>
       <c r="AB20">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-05-23T11:54:43.640Z</t>
+          <t>2026-05-23T12:37:54.469Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:09.543Z</t>
+          <t>2026-05-23T12:38:20.310Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -8263,13 +8263,13 @@
         </is>
       </c>
       <c r="J22">
-        <v>2.098</v>
+        <v>2.108</v>
       </c>
       <c r="K22">
-        <v>3.577</v>
+        <v>3.564</v>
       </c>
       <c r="L22">
-        <v>3.135</v>
+        <v>3.12</v>
       </c>
       <c r="M22">
         <v>2.141</v>
@@ -8282,27 +8282,27 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>+0.043</t>
+          <t>+0.033</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.018</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>-0.188</t>
+          <t>-0.173</t>
         </is>
       </c>
       <c r="S22">
         <v>-0.769</v>
       </c>
       <c r="T22">
-        <v>1.032</v>
+        <v>1.043</v>
       </c>
       <c r="U22">
-        <v>1.326</v>
+        <v>1.313</v>
       </c>
       <c r="V22">
         <v>-0.754</v>
@@ -8320,12 +8320,12 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>+0.076</t>
+          <t>+0.065</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.118</t>
+          <t>-0.105</t>
         </is>
       </c>
       <c r="AB22">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:10.604Z</t>
+          <t>2026-05-23T12:38:21.369Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -8467,13 +8467,13 @@
         </is>
       </c>
       <c r="J23">
-        <v>1.85</v>
+        <v>1.854</v>
       </c>
       <c r="K23">
-        <v>3.715</v>
+        <v>3.707</v>
       </c>
       <c r="L23">
-        <v>3.755</v>
+        <v>3.745</v>
       </c>
       <c r="M23">
         <v>1.865</v>
@@ -8486,27 +8486,27 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>+0.015</t>
+          <t>+0.011</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.112</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>-0.106</t>
+          <t>-0.096</t>
         </is>
       </c>
       <c r="S23">
-        <v>-0.992</v>
+        <v>-0.973</v>
       </c>
       <c r="T23">
-        <v>0.996</v>
+        <v>0.978</v>
       </c>
       <c r="U23">
-        <v>1.418</v>
+        <v>1.435</v>
       </c>
       <c r="V23">
         <v>-0.95</v>
@@ -8519,17 +8519,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>+0.042</t>
+          <t>+0.023</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>+0.012</t>
+          <t>+0.03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.047</t>
+          <t>-0.064</t>
         </is>
       </c>
       <c r="AB23">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:11.670Z</t>
+          <t>2026-05-23T12:38:22.426Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -8674,7 +8674,7 @@
         <v>2.011</v>
       </c>
       <c r="K24">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="L24">
         <v>3.312</v>
@@ -8695,7 +8695,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>-0.042</t>
+          <t>-0.052</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -8746,27 +8746,27 @@
         <v>1.79</v>
       </c>
       <c r="AE24">
-        <v>3.46</v>
+        <v>3.58</v>
       </c>
       <c r="AF24">
         <v>3.55</v>
       </c>
       <c r="AG24">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
+          <t>+0.12</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:15.995Z</t>
+          <t>2026-05-23T12:38:26.764Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:12.736Z</t>
+          <t>2026-05-23T12:38:23.490Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -9079,13 +9079,13 @@
         </is>
       </c>
       <c r="J26">
-        <v>2.384</v>
+        <v>2.385</v>
       </c>
       <c r="K26">
-        <v>3.903</v>
+        <v>3.896</v>
       </c>
       <c r="L26">
-        <v>2.504</v>
+        <v>2.498</v>
       </c>
       <c r="M26">
         <v>2.31</v>
@@ -9098,27 +9098,27 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-0.074</t>
+          <t>-0.075</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-0.079</t>
+          <t>-0.072</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>+0.051</t>
+          <t>+0.057</t>
         </is>
       </c>
       <c r="S26">
         <v>-0.585</v>
       </c>
       <c r="T26">
-        <v>1.114</v>
+        <v>1.118</v>
       </c>
       <c r="U26">
-        <v>1.178</v>
+        <v>1.174</v>
       </c>
       <c r="V26">
         <v>-0.662</v>
@@ -9136,12 +9136,12 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>+0.002</t>
+          <t>-0.002</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-0.014</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AB26">
@@ -9274,7 +9274,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:14.312Z</t>
+          <t>2026-05-23T12:38:25.062Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9283,13 +9283,13 @@
         </is>
       </c>
       <c r="J27">
-        <v>1.368</v>
+        <v>1.371</v>
       </c>
       <c r="K27">
-        <v>5.614</v>
+        <v>5.628</v>
       </c>
       <c r="L27">
-        <v>6.446</v>
+        <v>6.385</v>
       </c>
       <c r="M27">
         <v>1.356</v>
@@ -9302,17 +9302,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-0.012</t>
+          <t>-0.015</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.374</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>+0.122</t>
+          <t>+0.183</t>
         </is>
       </c>
       <c r="S27">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-05-23T11:51:05.000Z</t>
+          <t>2026-05-23T12:36:42.000Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -9499,13 +9499,13 @@
         </is>
       </c>
       <c r="J28">
-        <v>3.509</v>
+        <v>3.485</v>
       </c>
       <c r="K28">
-        <v>3.627</v>
+        <v>3.611</v>
       </c>
       <c r="L28">
-        <v>2.016</v>
+        <v>2.027</v>
       </c>
       <c r="M28">
         <v>3.709</v>
@@ -9518,17 +9518,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>+0.2</t>
+          <t>+0.224</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>+0.228</t>
+          <t>+0.244</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>-0.133</t>
+          <t>-0.144</t>
         </is>
       </c>
       <c r="S28">
@@ -9541,27 +9541,27 @@
         <v>1.896</v>
       </c>
       <c r="V28">
-        <v>0.469</v>
+        <v>0.438</v>
       </c>
       <c r="W28">
-        <v>1.864</v>
+        <v>1.869</v>
       </c>
       <c r="X28">
-        <v>1.998</v>
+        <v>1.991</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>-0.047</t>
+          <t>-0.078</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>-0.071</t>
+          <t>-0.066</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>+0.102</t>
+          <t>+0.095</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-05-23T11:51:12.000Z</t>
+          <t>2026-05-23T12:36:49.000Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -9718,10 +9718,10 @@
         <v>1.711</v>
       </c>
       <c r="K29">
-        <v>3.85</v>
+        <v>3.825</v>
       </c>
       <c r="L29">
-        <v>4.727</v>
+        <v>4.753</v>
       </c>
       <c r="M29">
         <v>1.491</v>
@@ -9739,12 +9739,12 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>+0.405</t>
+          <t>+0.43</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>+1.374</t>
+          <t>+1.348</t>
         </is>
       </c>
       <c r="S29">
@@ -9757,27 +9757,27 @@
         <v>1.932</v>
       </c>
       <c r="V29">
-        <v>-0.797</v>
+        <v>-0.781</v>
       </c>
       <c r="W29">
-        <v>1.891</v>
+        <v>1.876</v>
       </c>
       <c r="X29">
-        <v>1.9</v>
+        <v>1.914</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>+0.265</t>
+          <t>+0.281</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>+0.098</t>
+          <t>+0.083</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-0.032</t>
+          <t>-0.018</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-05-23T11:51:13.000Z</t>
+          <t>2026-05-23T12:36:50.000Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9931,13 +9931,13 @@
         </is>
       </c>
       <c r="J30">
-        <v>1.898</v>
+        <v>1.936</v>
       </c>
       <c r="K30">
-        <v>3.503</v>
+        <v>3.462</v>
       </c>
       <c r="L30">
-        <v>4.139</v>
+        <v>4.009</v>
       </c>
       <c r="M30">
         <v>1.89</v>
@@ -9950,17 +9950,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-0.008</t>
+          <t>-0.046</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>+0.007</t>
+          <t>+0.048</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>-0.227</t>
+          <t>-0.097</t>
         </is>
       </c>
       <c r="S30">
@@ -9976,10 +9976,10 @@
         <v>-0.531</v>
       </c>
       <c r="W30">
-        <v>1.948</v>
+        <v>1.926</v>
       </c>
       <c r="X30">
-        <v>1.902</v>
+        <v>1.868</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -9988,12 +9988,12 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>+0.047</t>
+          <t>+0.025</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>+0.026</t>
+          <t>-0.008</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-05-23T11:55:15.525Z</t>
+          <t>2026-05-23T12:38:26.269Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -10147,13 +10147,13 @@
         </is>
       </c>
       <c r="J31">
-        <v>2.719</v>
+        <v>2.731</v>
       </c>
       <c r="K31">
         <v>2.719</v>
       </c>
       <c r="L31">
-        <v>3.111</v>
+        <v>3.101</v>
       </c>
       <c r="M31">
         <v>2.369</v>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.362</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>+0.328</t>
+          <t>+0.338</t>
         </is>
       </c>
       <c r="S31">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-05-23T11:54:28.000Z</t>
+          <t>2026-05-23T12:36:50.000Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -10363,13 +10363,13 @@
         </is>
       </c>
       <c r="J32">
-        <v>1.808</v>
+        <v>1.814</v>
       </c>
       <c r="K32">
-        <v>3.866</v>
+        <v>3.861</v>
       </c>
       <c r="L32">
-        <v>4.058</v>
+        <v>4.052</v>
       </c>
       <c r="M32">
         <v>1.831</v>
@@ -10382,17 +10382,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>+0.023</t>
+          <t>+0.017</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>-0.124</t>
+          <t>-0.119</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.164</t>
         </is>
       </c>
       <c r="S32">
@@ -10408,10 +10408,10 @@
         <v>-0.562</v>
       </c>
       <c r="W32">
-        <v>1.876</v>
+        <v>1.874</v>
       </c>
       <c r="X32">
-        <v>1.967</v>
+        <v>1.969</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -10420,12 +10420,12 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>-0.015</t>
+          <t>-0.017</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>+0.031</t>
+          <t>+0.033</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-05-23T11:51:13.000Z</t>
+          <t>2026-05-23T12:36:50.000Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -10579,13 +10579,13 @@
         </is>
       </c>
       <c r="J33">
-        <v>2.261</v>
+        <v>2.289</v>
       </c>
       <c r="K33">
-        <v>3.377</v>
+        <v>3.427</v>
       </c>
       <c r="L33">
-        <v>3.15</v>
+        <v>3.065</v>
       </c>
       <c r="M33">
         <v>2.04</v>
@@ -10598,17 +10598,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>-0.221</t>
+          <t>-0.249</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>+0.327</t>
+          <t>+0.277</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>+0.135</t>
+          <t>+0.22</t>
         </is>
       </c>
       <c r="S33">
@@ -10621,27 +10621,27 @@
         <v>1.901</v>
       </c>
       <c r="V33">
-        <v>-0.283</v>
+        <v>-0.25</v>
       </c>
       <c r="W33">
-        <v>1.867</v>
+        <v>1.932</v>
       </c>
       <c r="X33">
-        <v>1.865</v>
+        <v>1.863</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>+0.133</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>-0.073</t>
+          <t>-0.008</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>-0.036</t>
+          <t>-0.038</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-05-23T11:54:10.000Z</t>
+          <t>2026-05-23T12:36:32.000Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -10795,13 +10795,13 @@
         </is>
       </c>
       <c r="J34">
-        <v>2.183</v>
+        <v>2.188</v>
       </c>
       <c r="K34">
-        <v>3.529</v>
+        <v>3.524</v>
       </c>
       <c r="L34">
-        <v>2.995</v>
+        <v>2.985</v>
       </c>
       <c r="M34">
         <v>2.303</v>
@@ -10814,17 +10814,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>+0.12</t>
+          <t>+0.115</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.135</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>-0.191</t>
+          <t>-0.181</t>
         </is>
       </c>
       <c r="S34">
@@ -10840,10 +10840,10 @@
         <v>-0.281</v>
       </c>
       <c r="W34">
-        <v>1.964</v>
+        <v>1.958</v>
       </c>
       <c r="X34">
-        <v>1.861</v>
+        <v>1.864</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -10852,12 +10852,12 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>+0.163</t>
+          <t>+0.157</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-0.083</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-05-23T11:53:56.000Z</t>
+          <t>2026-05-23T12:36:18.000Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -11011,13 +11011,13 @@
         </is>
       </c>
       <c r="J35">
-        <v>2.131</v>
+        <v>2.069</v>
       </c>
       <c r="K35">
-        <v>3.32</v>
+        <v>3.387</v>
       </c>
       <c r="L35">
-        <v>3.266</v>
+        <v>3.369</v>
       </c>
       <c r="M35">
         <v>2.112</v>
@@ -11030,17 +11030,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>-0.019</t>
+          <t>+0.043</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>+0.04</t>
+          <t>-0.027</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>-0.106</t>
+          <t>-0.209</t>
         </is>
       </c>
       <c r="S35">
@@ -11053,27 +11053,27 @@
         <v>1.957</v>
       </c>
       <c r="V35">
-        <v>-0.3</v>
+        <v>-0.433</v>
       </c>
       <c r="W35">
-        <v>1.919</v>
+        <v>1.984</v>
       </c>
       <c r="X35">
-        <v>1.906</v>
+        <v>1.84</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>-0.033</t>
+          <t>-0.166</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>+0.061</t>
+          <t>+0.126</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>-0.051</t>
+          <t>-0.117</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-05-23T11:53:56.000Z</t>
+          <t>2026-05-23T12:36:18.000Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -11227,13 +11227,13 @@
         </is>
       </c>
       <c r="J36">
-        <v>1.908</v>
+        <v>1.921</v>
       </c>
       <c r="K36">
-        <v>3.322</v>
+        <v>3.321</v>
       </c>
       <c r="L36">
-        <v>3.982</v>
+        <v>3.932</v>
       </c>
       <c r="M36">
         <v>2.067</v>
@@ -11246,17 +11246,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>+0.159</t>
+          <t>+0.146</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-0.165</t>
+          <t>-0.164</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>-0.508</t>
+          <t>-0.458</t>
         </is>
       </c>
       <c r="S36">
@@ -11272,10 +11272,10 @@
         <v>-0.5</v>
       </c>
       <c r="W36">
-        <v>1.916</v>
+        <v>1.927</v>
       </c>
       <c r="X36">
-        <v>1.833</v>
+        <v>1.827</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -11284,12 +11284,12 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.009</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>-0.045</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-05-23T11:50:48.000Z</t>
+          <t>2026-05-23T12:36:26.000Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -11446,10 +11446,10 @@
         <v>2.023</v>
       </c>
       <c r="K37">
-        <v>3.571</v>
+        <v>3.57</v>
       </c>
       <c r="L37">
-        <v>3.272</v>
+        <v>3.274</v>
       </c>
       <c r="M37">
         <v>1.778</v>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>+0.276</t>
+          <t>+0.277</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>+0.618</t>
+          <t>+0.616</t>
         </is>
       </c>
       <c r="S37">
@@ -11488,10 +11488,10 @@
         <v>-0.3</v>
       </c>
       <c r="W37">
-        <v>1.855</v>
+        <v>1.85</v>
       </c>
       <c r="X37">
-        <v>1.966</v>
+        <v>1.971</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -11500,12 +11500,12 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.035</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>+0.043</t>
+          <t>+0.048</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-05-23T11:54:03.000Z</t>
+          <t>2026-05-23T12:36:27.000Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -11659,13 +11659,13 @@
         </is>
       </c>
       <c r="J38">
-        <v>1.87</v>
+        <v>1.874</v>
       </c>
       <c r="K38">
-        <v>3.481</v>
+        <v>3.471</v>
       </c>
       <c r="L38">
-        <v>3.899</v>
+        <v>3.89</v>
       </c>
       <c r="M38">
         <v>1.866</v>
@@ -11678,17 +11678,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>-0.008</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>+0.005</t>
+          <t>+0.015</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>-0.136</t>
+          <t>-0.127</t>
         </is>
       </c>
       <c r="S38">
@@ -11704,10 +11704,10 @@
         <v>-0.517</v>
       </c>
       <c r="W38">
-        <v>1.913</v>
+        <v>1.911</v>
       </c>
       <c r="X38">
-        <v>1.903</v>
+        <v>1.909</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -11716,12 +11716,12 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>-0.034</t>
+          <t>-0.036</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>+0.054</t>
+          <t>+0.06</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -11866,7 +11866,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-05-23T11:54:03.000Z</t>
+          <t>2026-05-23T12:36:27.000Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -11875,13 +11875,13 @@
         </is>
       </c>
       <c r="J39">
-        <v>1.608</v>
+        <v>1.615</v>
       </c>
       <c r="K39">
-        <v>3.76</v>
+        <v>3.748</v>
       </c>
       <c r="L39">
-        <v>5.25</v>
+        <v>5.205</v>
       </c>
       <c r="M39">
         <v>1.591</v>
@@ -11894,17 +11894,17 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>-0.017</t>
+          <t>-0.024</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>+0.008</t>
+          <t>+0.02</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>-0.187</t>
+          <t>-0.142</t>
         </is>
       </c>
       <c r="S39">
@@ -11920,10 +11920,10 @@
         <v>-0.75</v>
       </c>
       <c r="W39">
-        <v>1.819</v>
+        <v>1.825</v>
       </c>
       <c r="X39">
-        <v>1.943</v>
+        <v>1.936</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
@@ -11932,12 +11932,12 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>-0.089</t>
+          <t>-0.083</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>+0.117</t>
+          <t>+0.11</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-05-23T11:54:04.000Z</t>
+          <t>2026-05-23T12:36:27.000Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -12091,13 +12091,13 @@
         </is>
       </c>
       <c r="J40">
-        <v>2.501</v>
+        <v>2.473</v>
       </c>
       <c r="K40">
-        <v>3.429</v>
+        <v>3.427</v>
       </c>
       <c r="L40">
-        <v>2.575</v>
+        <v>2.609</v>
       </c>
       <c r="M40">
         <v>2.484</v>
@@ -12110,17 +12110,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>-0.017</t>
+          <t>+0.011</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.018</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>-0.043</t>
+          <t>-0.077</t>
         </is>
       </c>
       <c r="S40">
@@ -12136,10 +12136,10 @@
         <v>0.031</v>
       </c>
       <c r="W40">
-        <v>1.835</v>
+        <v>1.815</v>
       </c>
       <c r="X40">
-        <v>1.926</v>
+        <v>1.947</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -12148,12 +12148,12 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>+0.079</t>
+          <t>+0.1</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -12557,21 +12557,21 @@
         </is>
       </c>
       <c r="R2">
-        <v>2.704</v>
+        <v>2.714</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -15362,21 +15362,21 @@
         </is>
       </c>
       <c r="R19">
-        <v>2.633</v>
+        <v>2.629</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -19143,35 +19143,35 @@
         </is>
       </c>
       <c r="K2">
-        <v>0.4454</v>
+        <v>0.454</v>
       </c>
       <c r="L2">
-        <v>0.2859</v>
+        <v>0.2856</v>
       </c>
       <c r="M2">
-        <v>0.2686</v>
+        <v>0.2604</v>
       </c>
       <c r="N2">
-        <v>0.4454</v>
+        <v>0.454</v>
       </c>
       <c r="O2">
-        <v>0.2859</v>
+        <v>0.2856</v>
       </c>
       <c r="P2">
-        <v>0.2686</v>
+        <v>0.2604</v>
       </c>
       <c r="Q2">
-        <v>0.5477</v>
+        <v>0.566</v>
       </c>
       <c r="R2">
-        <v>0.2382</v>
+        <v>0.2321</v>
       </c>
       <c r="S2">
-        <v>0.2141</v>
+        <v>0.202</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1-1:11.7% / 1-0:11.5% / 2-0:10.2%</t>
+          <t>1-0:11.8% / 1-1:11.3% / 2-0:10.5%</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -19180,7 +19180,7 @@
         </is>
       </c>
       <c r="V2">
-        <v>37.67</v>
+        <v>39.09</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         </is>
       </c>
       <c r="X2">
-        <v>-0.1137</v>
+        <v>-0.1147</v>
       </c>
       <c r="Y2">
         <v>0</v>
@@ -21234,35 +21234,35 @@
         </is>
       </c>
       <c r="K19">
-        <v>0.3917</v>
+        <v>0.3919</v>
       </c>
       <c r="L19">
-        <v>0.3052</v>
+        <v>0.3108</v>
       </c>
       <c r="M19">
-        <v>0.3031</v>
+        <v>0.2972</v>
       </c>
       <c r="N19">
-        <v>0.3917</v>
+        <v>0.3919</v>
       </c>
       <c r="O19">
-        <v>0.3052</v>
+        <v>0.3108</v>
       </c>
       <c r="P19">
-        <v>0.3031</v>
+        <v>0.2972</v>
       </c>
       <c r="Q19">
-        <v>0.4522</v>
+        <v>0.4561</v>
       </c>
       <c r="R19">
-        <v>0.2582</v>
+        <v>0.2581</v>
       </c>
       <c r="S19">
-        <v>0.2897</v>
+        <v>0.2859</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1-1:12.3% / 1-0:10.7% / 2-1:8.9%</t>
+          <t>1-1:12.3% / 1-0:10.7% / 2-1:9.1%</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -21271,7 +21271,7 @@
         </is>
       </c>
       <c r="V19">
-        <v>27.24</v>
+        <v>26.77</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         </is>
       </c>
       <c r="X19">
-        <v>-0.1148</v>
+        <v>-0.1143</v>
       </c>
       <c r="Y19">
         <v>0</v>

--- a/data/exports/football-recommendations-2026-05-23.xlsx
+++ b/data/exports/football-recommendations-2026-05-23.xlsx
@@ -428,7 +428,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:25.061Z</t>
+          <t>2026-05-23T12:46:30.118Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:25.061Z</t>
+          <t>2026-05-23T12:46:30.118Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:15.009Z</t>
+          <t>2026-05-23T12:46:19.455Z</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -4591,13 +4591,13 @@
         </is>
       </c>
       <c r="J4">
-        <v>2.074</v>
+        <v>2.075</v>
       </c>
       <c r="K4">
         <v>3.581</v>
       </c>
       <c r="L4">
-        <v>3.211</v>
+        <v>3.199</v>
       </c>
       <c r="M4">
         <v>1.869</v>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-0.205</t>
+          <t>-0.206</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -4620,17 +4620,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>+0.496</t>
+          <t>+0.508</t>
         </is>
       </c>
       <c r="S4">
-        <v>-1.042</v>
+        <v>-1.062</v>
       </c>
       <c r="T4">
-        <v>1.104</v>
+        <v>1.125</v>
       </c>
       <c r="U4">
-        <v>1.518</v>
+        <v>1.498</v>
       </c>
       <c r="V4">
         <v>-1.338</v>
@@ -4643,17 +4643,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-0.296</t>
+          <t>-0.276</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>+0.008</t>
+          <t>-0.013</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>+0.058</t>
+          <t>+0.078</t>
         </is>
       </c>
       <c r="AB4">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:16.065Z</t>
+          <t>2026-05-23T12:46:20.525Z</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -4795,13 +4795,13 @@
         </is>
       </c>
       <c r="J5">
-        <v>2.454</v>
+        <v>2.447</v>
       </c>
       <c r="K5">
         <v>3.431</v>
       </c>
       <c r="L5">
-        <v>2.636</v>
+        <v>2.641</v>
       </c>
       <c r="M5">
         <v>2.472</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>+0.018</t>
+          <t>+0.025</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-0.069</t>
+          <t>-0.074</t>
         </is>
       </c>
       <c r="S5">
-        <v>-0.523</v>
+        <v>-0.562</v>
       </c>
       <c r="T5">
-        <v>1.094</v>
+        <v>1.139</v>
       </c>
       <c r="U5">
-        <v>1.221</v>
+        <v>1.197</v>
       </c>
       <c r="V5">
         <v>-0.554</v>
@@ -4847,17 +4847,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>+0.008</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>+0.054</t>
+          <t>+0.009</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.066</t>
+          <t>-0.042</t>
         </is>
       </c>
       <c r="AB5">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-23T12:37:54.468Z</t>
+          <t>2026-05-23T12:46:00.322Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-05-23T12:37:54.468Z</t>
+          <t>2026-05-23T12:46:00.322Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:25.062Z</t>
+          <t>2026-05-23T12:46:30.119Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:26.266Z</t>
+          <t>2026-05-23T12:46:31.397Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-05-23T12:37:54.468Z</t>
+          <t>2026-05-23T12:46:00.323Z</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:26.266Z</t>
+          <t>2026-05-23T12:46:31.397Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:26.267Z</t>
+          <t>2026-05-23T12:46:31.399Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:26.272Z</t>
+          <t>2026-05-23T12:46:31.406Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:17.123Z</t>
+          <t>2026-05-23T12:46:21.601Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6631,10 +6631,10 @@
         </is>
       </c>
       <c r="J14">
-        <v>1.467</v>
+        <v>1.466</v>
       </c>
       <c r="K14">
-        <v>4.373</v>
+        <v>4.372</v>
       </c>
       <c r="L14">
         <v>6.839</v>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.159</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -6667,10 +6667,10 @@
         <v>-1.792</v>
       </c>
       <c r="T14">
-        <v>0.969</v>
+        <v>0.968</v>
       </c>
       <c r="U14">
-        <v>2.252</v>
+        <v>2.258</v>
       </c>
       <c r="V14">
         <v>-1.769</v>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>+0.069</t>
+          <t>+0.07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.086</t>
+          <t>-0.092</t>
         </is>
       </c>
       <c r="AB14">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:26.269Z</t>
+          <t>2026-05-23T12:46:31.402Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:18.183Z</t>
+          <t>2026-05-23T12:46:22.675Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7039,13 +7039,13 @@
         </is>
       </c>
       <c r="J16">
-        <v>1.478</v>
+        <v>1.482</v>
       </c>
       <c r="K16">
-        <v>4.695</v>
+        <v>4.687</v>
       </c>
       <c r="L16">
-        <v>5.778</v>
+        <v>5.742</v>
       </c>
       <c r="M16">
         <v>1.435</v>
@@ -7058,27 +7058,27 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>-0.043</t>
+          <t>-0.047</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>-0.031</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>+0.2</t>
+          <t>+0.236</t>
         </is>
       </c>
       <c r="S16">
-        <v>-1.715</v>
+        <v>-1.677</v>
       </c>
       <c r="T16">
-        <v>1.034</v>
+        <v>0.998</v>
       </c>
       <c r="U16">
-        <v>1.611</v>
+        <v>1.642</v>
       </c>
       <c r="V16">
         <v>-1.815</v>
@@ -7091,17 +7091,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.138</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>+0.036</t>
+          <t>+0.072</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>+0.024</t>
+          <t>-0.007</t>
         </is>
       </c>
       <c r="AB16">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:26.272Z</t>
+          <t>2026-05-23T12:46:31.406Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-05-23T12:37:54.469Z</t>
+          <t>2026-05-23T12:46:00.323Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:26.270Z</t>
+          <t>2026-05-23T12:46:31.404Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:19.244Z</t>
+          <t>2026-05-23T12:46:23.749Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -7855,13 +7855,13 @@
         </is>
       </c>
       <c r="J20">
-        <v>3.251</v>
+        <v>3.252</v>
       </c>
       <c r="K20">
-        <v>3.955</v>
+        <v>3.954</v>
       </c>
       <c r="L20">
-        <v>1.998</v>
+        <v>1.997</v>
       </c>
       <c r="M20">
         <v>3.512</v>
@@ -7874,27 +7874,27 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>+0.261</t>
+          <t>+0.26</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>-0.015</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>-0.147</t>
+          <t>-0.146</t>
         </is>
       </c>
       <c r="S20">
         <v>-0.158</v>
       </c>
       <c r="T20">
-        <v>1.223</v>
+        <v>1.215</v>
       </c>
       <c r="U20">
-        <v>1.173</v>
+        <v>1.178</v>
       </c>
       <c r="V20">
         <v>-0.181</v>
@@ -7912,12 +7912,12 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>+0.176</t>
+          <t>+0.184</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.138</t>
+          <t>-0.143</t>
         </is>
       </c>
       <c r="AB20">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-05-23T12:37:54.469Z</t>
+          <t>2026-05-23T12:46:00.323Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:20.310Z</t>
+          <t>2026-05-23T12:46:24.807Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -8299,10 +8299,10 @@
         <v>-0.769</v>
       </c>
       <c r="T22">
-        <v>1.043</v>
+        <v>1.045</v>
       </c>
       <c r="U22">
-        <v>1.313</v>
+        <v>1.312</v>
       </c>
       <c r="V22">
         <v>-0.754</v>
@@ -8320,12 +8320,12 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>+0.065</t>
+          <t>+0.063</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.105</t>
+          <t>-0.104</t>
         </is>
       </c>
       <c r="AB22">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:21.369Z</t>
+          <t>2026-05-23T12:46:26.413Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -8503,10 +8503,10 @@
         <v>-0.973</v>
       </c>
       <c r="T23">
-        <v>0.978</v>
+        <v>0.979</v>
       </c>
       <c r="U23">
-        <v>1.435</v>
+        <v>1.434</v>
       </c>
       <c r="V23">
         <v>-0.95</v>
@@ -8524,12 +8524,12 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>+0.03</t>
+          <t>+0.029</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.064</t>
+          <t>-0.063</t>
         </is>
       </c>
       <c r="AB23">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:22.426Z</t>
+          <t>2026-05-23T12:46:27.520Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -8671,7 +8671,7 @@
         </is>
       </c>
       <c r="J24">
-        <v>2.011</v>
+        <v>2.005</v>
       </c>
       <c r="K24">
         <v>3.6</v>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>-0.114</t>
+          <t>-0.108</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:26.764Z</t>
+          <t>2026-05-23T12:46:31.905Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:23.490Z</t>
+          <t>2026-05-23T12:46:28.577Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
@@ -9274,7 +9274,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:25.062Z</t>
+          <t>2026-05-23T12:46:30.120Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9283,13 +9283,13 @@
         </is>
       </c>
       <c r="J27">
-        <v>1.371</v>
+        <v>1.369</v>
       </c>
       <c r="K27">
         <v>5.628</v>
       </c>
       <c r="L27">
-        <v>6.385</v>
+        <v>6.396</v>
       </c>
       <c r="M27">
         <v>1.356</v>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-0.015</t>
+          <t>-0.013</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>+0.183</t>
+          <t>+0.172</t>
         </is>
       </c>
       <c r="S27">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-05-23T12:36:42.000Z</t>
+          <t>2026-05-23T12:43:02.000Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -9499,13 +9499,13 @@
         </is>
       </c>
       <c r="J28">
-        <v>3.485</v>
+        <v>3.453</v>
       </c>
       <c r="K28">
-        <v>3.611</v>
+        <v>3.596</v>
       </c>
       <c r="L28">
-        <v>2.027</v>
+        <v>2.045</v>
       </c>
       <c r="M28">
         <v>3.709</v>
@@ -9518,17 +9518,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>+0.224</t>
+          <t>+0.256</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>+0.244</t>
+          <t>+0.259</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>-0.144</t>
+          <t>-0.162</t>
         </is>
       </c>
       <c r="S28">
@@ -9541,27 +9541,27 @@
         <v>1.896</v>
       </c>
       <c r="V28">
-        <v>0.438</v>
+        <v>0.406</v>
       </c>
       <c r="W28">
-        <v>1.869</v>
+        <v>1.908</v>
       </c>
       <c r="X28">
-        <v>1.991</v>
+        <v>1.957</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>-0.078</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>-0.066</t>
+          <t>-0.027</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>+0.095</t>
+          <t>+0.061</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-05-23T12:36:49.000Z</t>
+          <t>2026-05-23T12:43:10.000Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -9760,10 +9760,10 @@
         <v>-0.781</v>
       </c>
       <c r="W29">
-        <v>1.876</v>
+        <v>1.877</v>
       </c>
       <c r="X29">
-        <v>1.914</v>
+        <v>1.912</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -9772,12 +9772,12 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>+0.083</t>
+          <t>+0.084</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-0.018</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-05-23T12:36:50.000Z</t>
+          <t>2026-05-23T12:43:11.000Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9931,13 +9931,13 @@
         </is>
       </c>
       <c r="J30">
-        <v>1.936</v>
+        <v>1.937</v>
       </c>
       <c r="K30">
-        <v>3.462</v>
+        <v>3.46</v>
       </c>
       <c r="L30">
-        <v>4.009</v>
+        <v>4.006</v>
       </c>
       <c r="M30">
         <v>1.89</v>
@@ -9950,17 +9950,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-0.046</t>
+          <t>-0.047</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>+0.048</t>
+          <t>+0.05</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>-0.097</t>
+          <t>-0.094</t>
         </is>
       </c>
       <c r="S30">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-05-23T12:38:26.269Z</t>
+          <t>2026-05-23T12:46:31.401Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-05-23T12:36:50.000Z</t>
+          <t>2026-05-23T12:43:11.000Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-05-23T12:36:50.000Z</t>
+          <t>2026-05-23T12:43:11.000Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-05-23T12:36:32.000Z</t>
+          <t>2026-05-23T12:42:52.000Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-05-23T12:36:18.000Z</t>
+          <t>2026-05-23T12:42:38.000Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -11011,13 +11011,13 @@
         </is>
       </c>
       <c r="J35">
-        <v>2.069</v>
+        <v>2.064</v>
       </c>
       <c r="K35">
-        <v>3.387</v>
+        <v>3.392</v>
       </c>
       <c r="L35">
-        <v>3.369</v>
+        <v>3.377</v>
       </c>
       <c r="M35">
         <v>2.112</v>
@@ -11030,17 +11030,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>+0.043</t>
+          <t>+0.048</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>-0.027</t>
+          <t>-0.032</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>-0.209</t>
+          <t>-0.217</t>
         </is>
       </c>
       <c r="S35">
@@ -11056,10 +11056,10 @@
         <v>-0.433</v>
       </c>
       <c r="W35">
-        <v>1.984</v>
+        <v>1.987</v>
       </c>
       <c r="X35">
-        <v>1.84</v>
+        <v>1.839</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -11068,12 +11068,12 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>+0.126</t>
+          <t>+0.129</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>-0.117</t>
+          <t>-0.118</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-05-23T12:36:18.000Z</t>
+          <t>2026-05-23T12:42:38.000Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -11227,13 +11227,13 @@
         </is>
       </c>
       <c r="J36">
-        <v>1.921</v>
+        <v>1.92</v>
       </c>
       <c r="K36">
-        <v>3.321</v>
+        <v>3.318</v>
       </c>
       <c r="L36">
-        <v>3.932</v>
+        <v>3.934</v>
       </c>
       <c r="M36">
         <v>2.067</v>
@@ -11246,17 +11246,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>+0.146</t>
+          <t>+0.147</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-0.164</t>
+          <t>-0.161</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>-0.458</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="S36">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-05-23T12:36:26.000Z</t>
+          <t>2026-05-23T12:42:45.000Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -11443,13 +11443,13 @@
         </is>
       </c>
       <c r="J37">
-        <v>2.023</v>
+        <v>2.025</v>
       </c>
       <c r="K37">
-        <v>3.57</v>
+        <v>3.567</v>
       </c>
       <c r="L37">
-        <v>3.274</v>
+        <v>3.271</v>
       </c>
       <c r="M37">
         <v>1.778</v>
@@ -11462,17 +11462,17 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>-0.245</t>
+          <t>-0.247</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>+0.277</t>
+          <t>+0.28</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>+0.616</t>
+          <t>+0.619</t>
         </is>
       </c>
       <c r="S37">
@@ -11488,10 +11488,10 @@
         <v>-0.3</v>
       </c>
       <c r="W37">
-        <v>1.85</v>
+        <v>1.851</v>
       </c>
       <c r="X37">
-        <v>1.971</v>
+        <v>1.969</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -11500,12 +11500,12 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>-0.035</t>
+          <t>-0.034</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>+0.048</t>
+          <t>+0.046</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-05-23T12:36:27.000Z</t>
+          <t>2026-05-23T12:42:46.000Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -11866,7 +11866,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-05-23T12:36:27.000Z</t>
+          <t>2026-05-23T12:42:46.000Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -11878,7 +11878,7 @@
         <v>1.615</v>
       </c>
       <c r="K39">
-        <v>3.748</v>
+        <v>3.744</v>
       </c>
       <c r="L39">
         <v>5.205</v>
@@ -11899,7 +11899,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>+0.02</t>
+          <t>+0.024</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -11920,10 +11920,10 @@
         <v>-0.75</v>
       </c>
       <c r="W39">
-        <v>1.825</v>
+        <v>1.823</v>
       </c>
       <c r="X39">
-        <v>1.936</v>
+        <v>1.938</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
@@ -11932,12 +11932,12 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>-0.083</t>
+          <t>-0.085</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>+0.11</t>
+          <t>+0.112</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -12022,7 +12022,7 @@
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-05-23T12:36:27.000Z</t>
+          <t>2026-05-23T12:42:46.000Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
@@ -19257,7 +19257,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -19380,7 +19380,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K5">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -19995,12 +19995,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="K9">
@@ -20246,7 +20246,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K11">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -20487,7 +20487,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -20733,7 +20733,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -21102,7 +21102,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -21225,7 +21225,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -21353,7 +21353,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="K20">
@@ -21471,12 +21471,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K21">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -21963,7 +21963,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -22091,7 +22091,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K26">
@@ -22460,7 +22460,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="K29">
@@ -22578,7 +22578,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -22701,7 +22701,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -22947,7 +22947,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -23198,7 +23198,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K35">
@@ -23316,7 +23316,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -23439,7 +23439,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -23808,7 +23808,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">

--- a/data/exports/football-recommendations-2026-05-23.xlsx
+++ b/data/exports/football-recommendations-2026-05-23.xlsx
@@ -782,12 +782,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="U6">
-        <v>43.94</v>
+        <v>48.14</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="U7">
-        <v>39.07</v>
+        <v>43.27</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>盘口 -0.25，主水 1.95，客水 1.85</t>
+          <t>盘口 -0.25，主水 1.85，客水 1.93</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>盘口 -0.75，主水 1.92，客水 1.92</t>
+          <t>盘口 -1，主水 1.94，客水 1.9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>胜 2.62，平 3.6，负 2.13</t>
+          <t>胜 2.7，平 3.45，负 2.13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>盘口 -0.75，主水 2.05，客水 1.8</t>
+          <t>盘口 -0.75，主水 2.02，客水 1.82</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="U13">
-        <v>31.71</v>
+        <v>35.91</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="U15">
-        <v>16.66</v>
+        <v>20.86</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2123,12 +2123,12 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="U17">
-        <v>26.77</v>
+        <v>30.97</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2839,22 +2839,22 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="U23">
-        <v>61.06</v>
+        <v>65.26</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>39.07</v>
+        <v>43.27</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G7">
-        <v>16.66</v>
+        <v>20.86</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:11.619Z</t>
+          <t>2026-05-23T13:26:32.717Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -3942,13 +3942,13 @@
         </is>
       </c>
       <c r="J2">
-        <v>2.116</v>
+        <v>2.12</v>
       </c>
       <c r="K2">
         <v>3.556</v>
       </c>
       <c r="L2">
-        <v>3.122</v>
+        <v>3.113</v>
       </c>
       <c r="M2">
         <v>1.869</v>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-0.247</t>
+          <t>-0.251</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3971,17 +3971,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>+0.585</t>
+          <t>+0.594</t>
         </is>
       </c>
       <c r="S2">
         <v>-1.042</v>
       </c>
       <c r="T2">
-        <v>1.143</v>
+        <v>1.145</v>
       </c>
       <c r="U2">
-        <v>1.458</v>
+        <v>1.456</v>
       </c>
       <c r="V2">
         <v>-1.338</v>
@@ -3999,12 +3999,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.033</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>+0.118</t>
+          <t>+0.12</t>
         </is>
       </c>
       <c r="AB2">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:12.681Z</t>
+          <t>2026-05-23T13:26:33.829Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -4149,7 +4149,7 @@
         <v>2.416</v>
       </c>
       <c r="K3">
-        <v>3.451</v>
+        <v>3.445</v>
       </c>
       <c r="L3">
         <v>2.675</v>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-0.005</t>
+          <t>+0.001</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-05-23T13:23:52.911Z</t>
+          <t>2026-05-23T13:26:11.182Z</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-05-23T13:23:52.911Z</t>
+          <t>2026-05-23T13:26:11.182Z</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:22.192Z</t>
+          <t>2026-05-23T13:26:11.183Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -4858,17 +4858,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>0-1:6 / 1-1:6 / 0-2:7 / 1-2:7 / 0-0:8.75</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>负负:2.9 / 平负:4.3 / 平平:4.3 / 胜胜:7.2 / 平胜:8.5</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>中国体彩网竞彩足球计算器+CubeGoal public match filter API https://www.cubegoal.com/odds/84943.html</t>
+          <t>中国体彩网竞彩足球计算器</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -4907,7 +4907,7 @@
         </is>
       </c>
       <c r="AU6">
-        <v>43.94</v>
+        <v>48.14</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:23.653Z</t>
+          <t>2026-05-23T13:26:11.183Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -5062,17 +5062,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>1-1:6.75 / 1-2:7.5 / 0-1:8.75 / 2-1:9.5 / 0-2:10.5</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>负负:3.05 / 平负:5.25 / 胜胜:5.25 / 平平:5.4 / 平胜:7.5</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>中国体彩网竞彩足球计算器+CubeGoal public match filter API https://www.cubegoal.com/odds/84816.html</t>
+          <t>中国体彩网竞彩足球计算器</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="AU7">
-        <v>39.07</v>
+        <v>43.27</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-23T13:23:52.911Z</t>
+          <t>2026-05-23T13:26:11.183Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:23.654Z</t>
+          <t>2026-05-23T13:26:11.183Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -5406,19 +5406,19 @@
         <v>-0.25</v>
       </c>
       <c r="T9">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="U9">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="V9">
         <v>-0.25</v>
       </c>
       <c r="W9">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="X9">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AB9">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>中国体彩网竞彩足球计算器+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-23/doc-inhyvtiw5662178.shtml+CubeGoal public match filter API https://www.cubegoal.com/odds/84926.html</t>
+          <t>中国体彩网竞彩足球计算器+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-23/doc-inhyvtiw5662178.shtml</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:23.655Z</t>
+          <t>2026-05-23T13:26:11.183Z</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -5610,33 +5610,33 @@
         <v>-0.75</v>
       </c>
       <c r="T10">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="U10">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="V10">
-        <v>-0.75</v>
+        <v>-1</v>
       </c>
       <c r="W10">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X10">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AB10">
@@ -5649,22 +5649,22 @@
         <v>2.25</v>
       </c>
       <c r="AE10">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AF10">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AG10">
         <v>2.13</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>+0.11</t>
+          <t>+0.19</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>中国体彩网竞彩足球计算器+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-23/doc-inhyvtiw5662178.shtml+CubeGoal public match filter API https://www.cubegoal.com/odds/84813.html</t>
+          <t>中国体彩网竞彩足球计算器+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-23/doc-inhyvtiw5662178.shtml</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:23.660Z</t>
+          <t>2026-05-23T13:26:11.183Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5811,36 +5811,36 @@
         </is>
       </c>
       <c r="S11">
-        <v>-0.75</v>
+        <v>-0.5</v>
       </c>
       <c r="T11">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="U11">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="V11">
         <v>-0.75</v>
       </c>
       <c r="W11">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="X11">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AB11">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>中国体彩网竞彩足球计算器+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-23/doc-inhyvtiw5662178.shtml+CubeGoal public match filter API https://www.cubegoal.com/odds/84831.html</t>
+          <t>中国体彩网竞彩足球计算器+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-23/doc-inhyvtiw5662178.shtml</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:13.746Z</t>
+          <t>2026-05-23T13:26:34.946Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:23.657Z</t>
+          <t>2026-05-23T13:26:11.183Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -6286,17 +6286,17 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>1-1:6 / 2-1:7.75 / 1-0:8.5 / 1-2:8.75 / 0-1:10</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>胜胜:3.5 / 平平:4.9 / 平胜:5.1 / 负负:5.2 / 平负:6.5</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>中国体彩网竞彩足球计算器+CubeGoal public match filter API https://www.cubegoal.com/odds/84826.html</t>
+          <t>中国体彩网竞彩足球计算器</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="AU13">
-        <v>31.71</v>
+        <v>35.91</v>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:14.818Z</t>
+          <t>2026-05-23T13:26:36.063Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6390,13 +6390,13 @@
         </is>
       </c>
       <c r="J14">
-        <v>1.484</v>
+        <v>1.483</v>
       </c>
       <c r="K14">
-        <v>4.669</v>
+        <v>4.672</v>
       </c>
       <c r="L14">
-        <v>5.713</v>
+        <v>5.722</v>
       </c>
       <c r="M14">
         <v>1.435</v>
@@ -6409,27 +6409,27 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>-0.049</t>
+          <t>-0.048</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-0.013</t>
+          <t>-0.016</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>+0.265</t>
+          <t>+0.256</t>
         </is>
       </c>
       <c r="S14">
         <v>-1.677</v>
       </c>
       <c r="T14">
-        <v>1.008</v>
+        <v>1.007</v>
       </c>
       <c r="U14">
-        <v>1.638</v>
+        <v>1.642</v>
       </c>
       <c r="V14">
         <v>-1.815</v>
@@ -6447,12 +6447,12 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>+0.062</t>
+          <t>+0.063</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.003</t>
+          <t>-0.007</t>
         </is>
       </c>
       <c r="AB14">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:23.660Z</t>
+          <t>2026-05-23T13:26:11.183Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6694,17 +6694,17 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>1-1:5.3 / 1-0:5.5 / 0-0:5.75 / 0-1:6.5 / 2-1:8.25</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>平平:3.5 / 胜胜:4 / 平胜:5.2 / 负负:5.5 / 平负:6.5</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>中国体彩网竞彩足球计算器+CubeGoal public match filter API https://www.cubegoal.com/odds/84830.html</t>
+          <t>中国体彩网竞彩足球计算器</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="AU15">
-        <v>16.66</v>
+        <v>20.86</v>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-05-23T13:23:52.912Z</t>
+          <t>2026-05-23T13:26:11.183Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:23.659Z</t>
+          <t>2026-05-23T13:26:11.183Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7102,17 +7102,17 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>1-1:5.75 / 1-0:7.5 / 2-1:7.5 / 0-1:8.25 / 1-2:8.75</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>胜胜:3.85 / 平平:4.1 / 平胜:4.7 / 负负:5.2 / 平负:6.25</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>中国体彩网竞彩足球计算器+CubeGoal public match filter API https://www.cubegoal.com/odds/84828.html</t>
+          <t>中国体彩网竞彩足球计算器</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="AU17">
-        <v>26.77</v>
+        <v>30.97</v>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:15.902Z</t>
+          <t>2026-05-23T13:26:37.158Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-05-23T13:23:52.912Z</t>
+          <t>2026-05-23T13:26:11.183Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:16.972Z</t>
+          <t>2026-05-23T13:26:38.269Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:18.054Z</t>
+          <t>2026-05-23T13:26:39.391Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:19.138Z</t>
+          <t>2026-05-23T13:26:40.502Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:24.695Z</t>
+          <t>2026-05-23T13:26:11.183Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -8326,17 +8326,17 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>1-1:7 / 2-1:7 / 1-0:7.5 / 2-0:8 / 1-2:11</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>胜胜:2.55 / 平胜:4.25 / 平平:5.6 / 负负:7.7 / 平负:9.5</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>中国体彩网竞彩足球计算器+CubeGoal public match filter API https://www.cubegoal.com/odds/84844.html</t>
+          <t>中国体彩网竞彩足球计算器</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -8351,22 +8351,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
@@ -8375,7 +8375,7 @@
         </is>
       </c>
       <c r="AU23">
-        <v>61.06</v>
+        <v>65.26</v>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:20.208Z</t>
+          <t>2026-05-23T13:26:41.586Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -8667,36 +8667,36 @@
         </is>
       </c>
       <c r="S25">
-        <v>0.5</v>
+        <v>-1.531</v>
       </c>
       <c r="T25">
-        <v>2.02</v>
+        <v>1.906</v>
       </c>
       <c r="U25">
-        <v>1.82</v>
+        <v>1.906</v>
       </c>
       <c r="V25">
-        <v>0.5</v>
+        <v>-1.516</v>
       </c>
       <c r="W25">
-        <v>2.02</v>
+        <v>1.964</v>
       </c>
       <c r="X25">
-        <v>1.82</v>
+        <v>1.879</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.015</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.058</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.027</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-05-23T13:22:05.000Z</t>
+          <t>2026-05-23T13:25:23.000Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -8895,10 +8895,10 @@
         <v>0.313</v>
       </c>
       <c r="W26">
-        <v>1.944</v>
+        <v>1.949</v>
       </c>
       <c r="X26">
-        <v>1.918</v>
+        <v>1.909</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -8907,12 +8907,12 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>+0.009</t>
+          <t>+0.014</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>+0.022</t>
+          <t>+0.013</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-05-23T13:22:13.000Z</t>
+          <t>2026-05-23T13:25:30.000Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9111,10 +9111,10 @@
         <v>-0.719</v>
       </c>
       <c r="W27">
-        <v>1.892</v>
+        <v>1.895</v>
       </c>
       <c r="X27">
-        <v>1.954</v>
+        <v>1.951</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -9123,12 +9123,12 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>+0.099</t>
+          <t>+0.102</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>+0.022</t>
+          <t>+0.019</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -9227,7 +9227,7 @@
         </is>
       </c>
       <c r="AU27">
-        <v>39.07</v>
+        <v>43.27</v>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-05-23T13:22:14.000Z</t>
+          <t>2026-05-23T13:25:31.000Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:23.656Z</t>
+          <t>2026-05-23T13:25:31.000Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -9531,36 +9531,36 @@
         </is>
       </c>
       <c r="S29">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="T29">
-        <v>1.98</v>
+        <v>1.879</v>
       </c>
       <c r="U29">
-        <v>1.88</v>
+        <v>1.795</v>
       </c>
       <c r="V29">
-        <v>-0.5</v>
+        <v>-0.047</v>
       </c>
       <c r="W29">
-        <v>1.98</v>
+        <v>1.821</v>
       </c>
       <c r="X29">
-        <v>1.88</v>
+        <v>1.989</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.203</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.058</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.194</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-05-23T13:22:13.000Z</t>
+          <t>2026-05-23T13:25:31.000Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="AU30">
-        <v>16.66</v>
+        <v>20.86</v>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-05-23T13:22:13.000Z</t>
+          <t>2026-05-23T13:25:31.000Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-05-23T13:21:55.000Z</t>
+          <t>2026-05-23T13:25:14.000Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:22.192Z</t>
+          <t>2026-05-23T13:25:00.000Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -10395,36 +10395,36 @@
         </is>
       </c>
       <c r="S33">
-        <v>-0.5</v>
+        <v>-0.267</v>
       </c>
       <c r="T33">
-        <v>2.1</v>
+        <v>1.858</v>
       </c>
       <c r="U33">
-        <v>1.7</v>
+        <v>1.957</v>
       </c>
       <c r="V33">
-        <v>-0.5</v>
+        <v>-0.483</v>
       </c>
       <c r="W33">
-        <v>2.1</v>
+        <v>1.999</v>
       </c>
       <c r="X33">
-        <v>1.7</v>
+        <v>1.837</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.216</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.141</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:22.191Z</t>
+          <t>2026-05-23T13:25:00.000Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -10611,36 +10611,36 @@
         </is>
       </c>
       <c r="S34">
-        <v>-0.75</v>
+        <v>-0.406</v>
       </c>
       <c r="T34">
-        <v>2.1</v>
+        <v>1.936</v>
       </c>
       <c r="U34">
-        <v>1.7</v>
+        <v>1.872</v>
       </c>
       <c r="V34">
-        <v>-0.75</v>
+        <v>-0.5</v>
       </c>
       <c r="W34">
-        <v>2.1</v>
+        <v>1.904</v>
       </c>
       <c r="X34">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.094</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.032</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-05-23T13:21:48.000Z</t>
+          <t>2026-05-23T13:25:07.000Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -10794,7 +10794,7 @@
         </is>
       </c>
       <c r="J35">
-        <v>2.077</v>
+        <v>2.076</v>
       </c>
       <c r="K35">
         <v>3.54</v>
@@ -10813,7 +10813,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>-0.299</t>
+          <t>-0.298</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -10839,7 +10839,7 @@
         <v>-0.283</v>
       </c>
       <c r="W35">
-        <v>1.877</v>
+        <v>1.878</v>
       </c>
       <c r="X35">
         <v>1.94</v>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>-0.008</t>
+          <t>-0.007</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-05-23T13:21:48.000Z</t>
+          <t>2026-05-23T13:25:08.000Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-05-23T13:21:49.000Z</t>
+          <t>2026-05-23T13:25:08.000Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -11271,10 +11271,10 @@
         <v>-0.969</v>
       </c>
       <c r="W37">
-        <v>1.895</v>
+        <v>1.889</v>
       </c>
       <c r="X37">
-        <v>1.865</v>
+        <v>1.871</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>-0.013</t>
+          <t>-0.019</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>+0.039</t>
+          <t>+0.045</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-05-23T13:21:49.000Z</t>
+          <t>2026-05-23T13:25:08.000Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -11487,10 +11487,10 @@
         <v>0</v>
       </c>
       <c r="W38">
-        <v>1.818</v>
+        <v>1.819</v>
       </c>
       <c r="X38">
-        <v>1.947</v>
+        <v>1.946</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -11499,12 +11499,12 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>-0.027</t>
+          <t>-0.026</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>+0.099</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>主判断：主胜，防客胜；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.79）；赔率：资金/赔率支持首选（资金/赔率支持首选；亚盘变化-0.3）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，支撑大于风险</t>
+          <t>主判断：主胜，防客胜；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.79）；赔率：资金/赔率支持首选（资金/赔率支持首选；亚盘变化-0.3）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，支撑大于风险</t>
         </is>
       </c>
     </row>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>主判断：主胜，防客胜；冷门：中高（概率差过小）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.64）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.04）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防客胜；冷门：中高（概率差过小）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.64）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.04）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -12039,7 +12039,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.88）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.25）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.88）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.25）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -12139,7 +12139,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.75）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.75）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -12200,7 +12200,7 @@
         </is>
       </c>
       <c r="L6">
-        <v>43.94</v>
+        <v>48.14</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>主判断：客胜，防平局；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.75）；赔率：首选热度走弱（首选热度走弱；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
+          <t>主判断：客胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.75）；赔率：首选热度走弱（首选热度走弱；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12300,7 @@
         </is>
       </c>
       <c r="L7">
-        <v>39.07</v>
+        <v>43.27</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>主判断：客胜，防主胜；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.74）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
+          <t>主判断：客胜，防主胜；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.74）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -12439,7 +12439,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.97）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：强信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.97）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：强信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>主判断：主胜，防客胜；冷门：中高（备选赔付不高，市场不排除）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.71）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防客胜；冷门：中高（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.71）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>常规｜赔率变化平稳；亚盘变化0</t>
+          <t>常规｜赔率变化平稳；亚盘变化-0.25</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.89）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.89）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.25）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -12734,12 +12734,12 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>常规｜赔率变化平稳；亚盘变化0</t>
+          <t>常规｜赔率变化平稳；亚盘变化-0.25</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.82）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.82）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.25）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -12839,7 +12839,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.92）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化+0.02）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：强信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.92）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化+0.02）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：强信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -12900,7 +12900,7 @@
         </is>
       </c>
       <c r="L13">
-        <v>31.71</v>
+        <v>35.91</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：中高（备选赔付不高，市场不排除）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.66）；赔率：资金/赔率支持首选（资金/赔率支持首选；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：中高（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.66）；赔率：资金/赔率支持首选（资金/赔率支持首选；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.92）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.14）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：强信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.92）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.14）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：强信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -13100,7 +13100,7 @@
         </is>
       </c>
       <c r="L15">
-        <v>16.66</v>
+        <v>20.86</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：中高（概率差过小）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.57）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：中高（概率差过小）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.57）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -13239,7 +13239,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.83）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.25）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.83）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.25）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -13296,11 +13296,11 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="L17">
-        <v>26.77</v>
+        <v>30.97</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：中高（备选赔付不高，市场不排除）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.63）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：中高（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.63）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -13439,7 +13439,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>主判断：客胜，防主胜；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.78）；赔率：资金/赔率支持首选（资金/赔率支持首选；亚盘变化-0.02）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，支撑大于风险</t>
+          <t>主判断：客胜，防主胜；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.78）；赔率：资金/赔率支持首选（资金/赔率支持首选；亚盘变化-0.02）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，支撑大于风险</t>
         </is>
       </c>
     </row>
@@ -13539,7 +13539,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>主判断：主胜，防客胜；冷门：中高（备选赔付不高，市场不排除）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.67）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防客胜；冷门：中高（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.67）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>主判断：主胜，防客胜；冷门：中高（备选赔付不高，市场不排除）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.70）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化+0.01）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防客胜；冷门：中高（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.70）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化+0.01）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -13739,7 +13739,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.78）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化+0.02）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.78）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化+0.02）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -13839,7 +13839,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.76）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.02）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.76）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.02）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -13891,16 +13891,16 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="L23">
-        <v>61.06</v>
+        <v>65.26</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.85）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.85）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>主判断：主胜，防客胜；冷门：中高（概率差过小）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.67）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.08）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防客胜；冷门：中高（概率差过小）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.67）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.08）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -14134,12 +14134,12 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>常规｜赔率变化平稳；亚盘变化0</t>
+          <t>常规｜赔率变化平稳；亚盘变化+0.02</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.95）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：强信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.95）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化+0.02）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：强信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（备选赔付不高，市场不排除）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.79）；赔率：首选热度走弱（首选热度走弱；亚盘变化-0.2）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.79）；赔率：首选热度走弱（首选热度走弱；亚盘变化-0.2）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -14300,7 +14300,7 @@
         </is>
       </c>
       <c r="L27">
-        <v>39.07</v>
+        <v>43.27</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>主判断：客胜，防主胜；冷门：低（备选赔付不高，市场不排除）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.91）；赔率：首选热度走弱（首选热度走弱；亚盘变化+0.34）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：客胜，防主胜；冷门：低（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.91）；赔率：首选热度走弱（首选热度走弱；亚盘变化+0.34）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -14439,7 +14439,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.77）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.77）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -14534,12 +14534,12 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>常规｜资金/赔率支持首选；亚盘变化0</t>
+          <t>常规｜资金/赔率支持首选；亚盘变化+0.2</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（备选赔付不高，市场不排除）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.62）；赔率：资金/赔率支持首选（资金/赔率支持首选；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.62）；赔率：资金/赔率支持首选（资金/赔率支持首选；亚盘变化+0.2）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -14600,7 +14600,7 @@
         </is>
       </c>
       <c r="L30">
-        <v>16.66</v>
+        <v>20.86</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：高（概率差过小）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.80）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.02）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：高（概率差过小）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.80）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.02）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.74）；赔率：资金/赔率支持首选（资金/赔率支持首选；亚盘变化+0.13）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，支撑大于风险</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.74）；赔率：资金/赔率支持首选（资金/赔率支持首选；亚盘变化+0.13）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，支撑大于风险</t>
         </is>
       </c>
     </row>
@@ -14839,7 +14839,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>主判断：主胜，防客胜；冷门：中高（备选赔付不高，市场不排除）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.66）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.19）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防客胜；冷门：中高（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.66）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.19）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -14934,12 +14934,12 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>常规｜首选热度走弱；亚盘变化0</t>
+          <t>常规｜首选热度走弱；亚盘变化-0.22</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>主判断：主胜，防客胜；冷门：低（备选赔付不高，市场不排除）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.70）；赔率：首选热度走弱（首选热度走弱；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防客胜；冷门：低（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.70）；赔率：首选热度走弱（首选热度走弱；亚盘变化-0.22）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -15034,12 +15034,12 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>常规｜首选热度走弱；亚盘变化0</t>
+          <t>常规｜首选热度走弱；亚盘变化-0.09</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（备选赔付不高，市场不排除）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.70）；赔率：首选热度走弱（首选热度走弱；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.70）；赔率：首选热度走弱（首选热度走弱；亚盘变化-0.09）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>主判断：主胜，防客胜；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.81）；赔率：资金/赔率支持首选（资金/赔率支持首选；亚盘变化+0.3）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
+          <t>主判断：主胜，防客胜；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.81）；赔率：资金/赔率支持首选（资金/赔率支持首选；亚盘变化+0.3）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -15239,7 +15239,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.77）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化+0.02）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.77）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化+0.02）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.87）；赔率：首选热度走弱（首选热度走弱；亚盘变化-0.09）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.87）；赔率：首选热度走弱（首选热度走弱；亚盘变化-0.09）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -15439,7 +15439,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>主判断：主胜，防客胜；冷门：中高（概率差过小）；大小球：undefined（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.63）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化+0.09）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防客胜；冷门：中高（概率差过小）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.63）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化+0.09）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -22469,12 +22469,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -22525,7 +22525,7 @@
         </is>
       </c>
       <c r="V6">
-        <v>43.94</v>
+        <v>48.14</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -22607,7 +22607,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="K7">
@@ -22648,7 +22648,7 @@
         </is>
       </c>
       <c r="V7">
-        <v>39.07</v>
+        <v>43.27</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         </is>
       </c>
       <c r="V13">
-        <v>31.71</v>
+        <v>35.91</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -23576,12 +23576,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -23632,7 +23632,7 @@
         </is>
       </c>
       <c r="V15">
-        <v>16.66</v>
+        <v>20.86</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -23832,12 +23832,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K17">
@@ -23878,7 +23878,7 @@
         </is>
       </c>
       <c r="V17">
-        <v>26.77</v>
+        <v>30.97</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -24560,22 +24560,22 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K23">
@@ -24616,7 +24616,7 @@
         </is>
       </c>
       <c r="V23">
-        <v>61.06</v>
+        <v>65.26</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -25108,7 +25108,7 @@
         </is>
       </c>
       <c r="V27">
-        <v>39.07</v>
+        <v>43.27</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         </is>
       </c>
       <c r="V30">
-        <v>16.66</v>
+        <v>20.86</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>

--- a/data/exports/football-recommendations-2026-05-23.xlsx
+++ b/data/exports/football-recommendations-2026-05-23.xlsx
@@ -510,7 +510,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>胜 2.6，平 3.2，负 2.32</t>
+          <t>胜 2.4，平 3.2，负 2.5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>胜 3.97，平 3.05，负 1.82</t>
+          <t>胜 4.1，平 3.12，负 1.77</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>胜 1.75，平 3.42，负 3.76</t>
+          <t>胜 1.79，平 3.4，负 3.62</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -767,27 +767,27 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="U6">
-        <v>48.14</v>
+        <v>46.74</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="W6">
-        <v>-0.1144</v>
+        <v>-0.1146</v>
       </c>
       <c r="X6">
         <v>0</v>
@@ -863,7 +863,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>胜 3.05，平 3.5，负 1.94</t>
+          <t>胜 2.95，平 3.5，负 1.98</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>胜 1.65，平 3.8，负 3.85</t>
+          <t>胜 1.62，平 3.85，负 4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="U7">
-        <v>43.27</v>
+        <v>36.66</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="W7">
-        <v>-0.1144</v>
+        <v>-0.1149</v>
       </c>
       <c r="X7">
         <v>0</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>胜 1.74，平 4.25，负 3.13</t>
+          <t>胜 1.7，平 4.5，负 3.13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>盘口 -0.25，主水 1.85，客水 1.93</t>
+          <t>盘口 -0.25，主水 1.95，客水 1.85</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>盘口 -1，主水 1.94，客水 1.9</t>
+          <t>盘口 -0.75，主水 1.92，客水 1.92</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>胜 2.7，平 3.45，负 2.13</t>
+          <t>胜 2.8，平 3.45，负 2.08</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>盘口 -0.75，主水 2.02，客水 1.82</t>
+          <t>盘口 -0.75，主水 2.05，客水 1.8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="U13">
-        <v>35.91</v>
+        <v>31.71</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="U15">
-        <v>20.86</v>
+        <v>16.66</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2123,12 +2123,12 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>主胜-平局</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="U17">
-        <v>30.97</v>
+        <v>26.77</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2839,22 +2839,22 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>主胜-平局</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="U23">
-        <v>65.26</v>
+        <v>61.06</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -3169,11 +3169,11 @@
         </is>
       </c>
       <c r="G4">
-        <v>43.27</v>
+        <v>36.66</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>概率差 17%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：意甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六013 胜平负方向强制一致</t>
+          <t>概率差 15%；14场严格定胆规则：未入强胆池，降为覆盖；经模型综合分析：意甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六013 胜平负方向强制一致</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G7">
-        <v>20.86</v>
+        <v>16.66</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:32.717Z</t>
+          <t>2026-05-23T14:00:42.575Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -3942,13 +3942,13 @@
         </is>
       </c>
       <c r="J2">
-        <v>2.12</v>
+        <v>2.121</v>
       </c>
       <c r="K2">
-        <v>3.556</v>
+        <v>3.547</v>
       </c>
       <c r="L2">
-        <v>3.113</v>
+        <v>3.112</v>
       </c>
       <c r="M2">
         <v>1.869</v>
@@ -3961,27 +3961,27 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-0.251</t>
+          <t>-0.252</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>+0.242</t>
+          <t>+0.251</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>+0.594</t>
+          <t>+0.595</t>
         </is>
       </c>
       <c r="S2">
-        <v>-1.042</v>
+        <v>-1.019</v>
       </c>
       <c r="T2">
-        <v>1.145</v>
+        <v>1.138</v>
       </c>
       <c r="U2">
-        <v>1.456</v>
+        <v>1.448</v>
       </c>
       <c r="V2">
         <v>-1.338</v>
@@ -3994,17 +3994,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-0.296</t>
+          <t>-0.319</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.033</t>
+          <t>-0.026</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>+0.12</t>
+          <t>+0.128</t>
         </is>
       </c>
       <c r="AB2">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:33.829Z</t>
+          <t>2026-05-23T14:00:43.640Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -4146,13 +4146,13 @@
         </is>
       </c>
       <c r="J3">
-        <v>2.416</v>
+        <v>2.394</v>
       </c>
       <c r="K3">
-        <v>3.445</v>
+        <v>3.515</v>
       </c>
       <c r="L3">
-        <v>2.675</v>
+        <v>2.657</v>
       </c>
       <c r="M3">
         <v>2.472</v>
@@ -4165,27 +4165,27 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>+0.056</t>
+          <t>+0.078</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>+0.001</t>
+          <t>-0.069</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>-0.108</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="S3">
-        <v>-0.512</v>
+        <v>-0.523</v>
       </c>
       <c r="T3">
-        <v>1.046</v>
+        <v>1.033</v>
       </c>
       <c r="U3">
-        <v>1.275</v>
+        <v>1.285</v>
       </c>
       <c r="V3">
         <v>-0.554</v>
@@ -4198,17 +4198,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-0.042</t>
+          <t>-0.031</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>+0.102</t>
+          <t>+0.115</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB3">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:11.182Z</t>
+          <t>2026-05-23T14:00:20.622Z</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -4425,17 +4425,17 @@
         <v>2.15</v>
       </c>
       <c r="AE4">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AF4">
         <v>3.2</v>
       </c>
       <c r="AG4">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>+0.17</t>
+          <t>+0.35</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:11.182Z</t>
+          <t>2026-05-23T14:00:20.622Z</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:11.183Z</t>
+          <t>2026-05-23T14:00:52.590Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -4767,27 +4767,27 @@
         <v>1.62</v>
       </c>
       <c r="M6">
-        <v>3.97</v>
+        <v>4.1</v>
       </c>
       <c r="N6">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="O6">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>+0.2</t>
+          <t>+0.15</t>
         </is>
       </c>
       <c r="S6">
@@ -4833,42 +4833,42 @@
         <v>3.05</v>
       </c>
       <c r="AE6">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AF6">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AG6">
-        <v>3.76</v>
+        <v>3.62</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>+0.04</t>
+          <t>+0.02</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>+0.71</t>
+          <t>+0.57</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0-1:6 / 1-1:6 / 0-2:7 / 1-2:7 / 0-0:8.75</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>负负:2.9 / 平负:4.3 / 平平:4.3 / 胜胜:7.2 / 平胜:8.5</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>中国体彩网竞彩足球计算器</t>
+          <t>中国体彩网竞彩足球计算器+CubeGoal public match filter API https://www.cubegoal.com/odds/84943.html</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -4907,7 +4907,7 @@
         </is>
       </c>
       <c r="AU6">
-        <v>48.14</v>
+        <v>46.74</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:11.183Z</t>
+          <t>2026-05-23T14:00:53.678Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -4971,17 +4971,17 @@
         <v>2</v>
       </c>
       <c r="M7">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="N7">
         <v>3.5</v>
       </c>
       <c r="O7">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>+0.17</t>
+          <t>+0.07</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="S7">
@@ -5037,42 +5037,42 @@
         <v>4</v>
       </c>
       <c r="AE7">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AF7">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AG7">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>+0.04</t>
+          <t>+0.01</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1-1:6.75 / 1-2:7.5 / 0-1:8.75 / 2-1:9.5 / 0-2:10.5</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>负负:3.05 / 平负:5.25 / 胜胜:5.25 / 平平:5.4 / 平胜:7.5</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>中国体彩网竞彩足球计算器</t>
+          <t>中国体彩网竞彩足球计算器+CubeGoal public match filter API https://www.cubegoal.com/odds/84816.html</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="AU7">
-        <v>43.27</v>
+        <v>36.66</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:11.183Z</t>
+          <t>2026-05-23T14:00:20.622Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -5241,22 +5241,22 @@
         <v>2.95</v>
       </c>
       <c r="AE8">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AF8">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AG8">
         <v>3.13</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:11.183Z</t>
+          <t>2026-05-23T14:00:53.678Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -5406,20 +5406,20 @@
         <v>-0.25</v>
       </c>
       <c r="T9">
+        <v>1.95</v>
+      </c>
+      <c r="U9">
         <v>1.85</v>
-      </c>
-      <c r="U9">
-        <v>2</v>
       </c>
       <c r="V9">
         <v>-0.25</v>
       </c>
       <c r="W9">
+        <v>1.95</v>
+      </c>
+      <c r="X9">
         <v>1.85</v>
       </c>
-      <c r="X9">
-        <v>1.93</v>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
           <t>0</t>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB9">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>中国体彩网竞彩足球计算器+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-23/doc-inhyvtiw5662178.shtml</t>
+          <t>中国体彩网竞彩足球计算器+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-23/doc-inhyvtiw5662178.shtml+CubeGoal public match filter API https://www.cubegoal.com/odds/84926.html</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:11.183Z</t>
+          <t>2026-05-23T14:00:53.680Z</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -5610,33 +5610,33 @@
         <v>-0.75</v>
       </c>
       <c r="T10">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="U10">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>-0.75</v>
       </c>
       <c r="W10">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X10">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>+0.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB10">
@@ -5649,17 +5649,17 @@
         <v>2.25</v>
       </c>
       <c r="AE10">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AF10">
         <v>3.45</v>
       </c>
       <c r="AG10">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>+0.19</t>
+          <t>+0.29</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>中国体彩网竞彩足球计算器+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-23/doc-inhyvtiw5662178.shtml</t>
+          <t>中国体彩网竞彩足球计算器+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-23/doc-inhyvtiw5662178.shtml+CubeGoal public match filter API https://www.cubegoal.com/odds/84813.html</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:11.183Z</t>
+          <t>2026-05-23T14:00:53.688Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5811,36 +5811,36 @@
         </is>
       </c>
       <c r="S11">
-        <v>-0.5</v>
+        <v>-0.75</v>
       </c>
       <c r="T11">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="U11">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="V11">
         <v>-0.75</v>
       </c>
       <c r="W11">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="X11">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>+0.24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB11">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>中国体彩网竞彩足球计算器+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-23/doc-inhyvtiw5662178.shtml</t>
+          <t>中国体彩网竞彩足球计算器+Sina euro-asian contrast https://sports.sina.com.cn/l/2026-05-23/doc-inhyvtiw5662178.shtml+CubeGoal public match filter API https://www.cubegoal.com/odds/84831.html</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:34.946Z</t>
+          <t>2026-05-23T14:00:44.708Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5982,13 +5982,13 @@
         </is>
       </c>
       <c r="J12">
-        <v>1.462</v>
+        <v>1.465</v>
       </c>
       <c r="K12">
-        <v>4.38</v>
+        <v>4.371</v>
       </c>
       <c r="L12">
-        <v>6.89</v>
+        <v>6.835</v>
       </c>
       <c r="M12">
         <v>1.466</v>
@@ -6001,27 +6001,27 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>+0.004</t>
+          <t>+0.001</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>-0.167</t>
+          <t>-0.158</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>-0.471</t>
+          <t>-0.416</t>
         </is>
       </c>
       <c r="S12">
         <v>-1.792</v>
       </c>
       <c r="T12">
-        <v>0.965</v>
+        <v>0.964</v>
       </c>
       <c r="U12">
-        <v>2.263</v>
+        <v>2.26</v>
       </c>
       <c r="V12">
         <v>-1.769</v>
@@ -6039,12 +6039,12 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>+0.073</t>
+          <t>+0.074</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.097</t>
+          <t>-0.094</t>
         </is>
       </c>
       <c r="AB12">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:11.183Z</t>
+          <t>2026-05-23T14:00:53.683Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -6286,17 +6286,17 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1-1:6 / 2-1:7.75 / 1-0:8.5 / 1-2:8.75 / 0-1:10</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>胜胜:3.5 / 平平:4.9 / 平胜:5.1 / 负负:5.2 / 平负:6.5</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>中国体彩网竞彩足球计算器</t>
+          <t>中国体彩网竞彩足球计算器+CubeGoal public match filter API https://www.cubegoal.com/odds/84826.html</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="AU13">
-        <v>35.91</v>
+        <v>31.71</v>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:36.063Z</t>
+          <t>2026-05-23T14:00:45.772Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6390,13 +6390,13 @@
         </is>
       </c>
       <c r="J14">
-        <v>1.483</v>
+        <v>1.487</v>
       </c>
       <c r="K14">
-        <v>4.672</v>
+        <v>4.655</v>
       </c>
       <c r="L14">
-        <v>5.722</v>
+        <v>5.638</v>
       </c>
       <c r="M14">
         <v>1.435</v>
@@ -6409,27 +6409,27 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>-0.048</t>
+          <t>-0.052</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>+0.001</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>+0.256</t>
+          <t>+0.34</t>
         </is>
       </c>
       <c r="S14">
-        <v>-1.677</v>
+        <v>-1.638</v>
       </c>
       <c r="T14">
-        <v>1.007</v>
+        <v>0.985</v>
       </c>
       <c r="U14">
-        <v>1.642</v>
+        <v>1.664</v>
       </c>
       <c r="V14">
         <v>-1.815</v>
@@ -6442,17 +6442,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>-0.138</t>
+          <t>-0.177</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>+0.063</t>
+          <t>+0.085</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.007</t>
+          <t>-0.029</t>
         </is>
       </c>
       <c r="AB14">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:11.183Z</t>
+          <t>2026-05-23T14:00:53.687Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6694,17 +6694,17 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1-1:5.3 / 1-0:5.5 / 0-0:5.75 / 0-1:6.5 / 2-1:8.25</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>平平:3.5 / 胜胜:4 / 平胜:5.2 / 负负:5.5 / 平负:6.5</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>中国体彩网竞彩足球计算器</t>
+          <t>中国体彩网竞彩足球计算器+CubeGoal public match filter API https://www.cubegoal.com/odds/84830.html</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="AU15">
-        <v>20.86</v>
+        <v>16.66</v>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:11.183Z</t>
+          <t>2026-05-23T14:00:20.623Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:11.183Z</t>
+          <t>2026-05-23T14:00:53.686Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7102,17 +7102,17 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1-1:5.75 / 1-0:7.5 / 2-1:7.5 / 0-1:8.25 / 1-2:8.75</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>胜胜:3.85 / 平平:4.1 / 平胜:4.7 / 负负:5.2 / 平负:6.25</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>中国体彩网竞彩足球计算器</t>
+          <t>中国体彩网竞彩足球计算器+CubeGoal public match filter API https://www.cubegoal.com/odds/84828.html</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>主胜-平局</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="AU17">
-        <v>30.97</v>
+        <v>26.77</v>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:37.158Z</t>
+          <t>2026-05-23T14:00:46.841Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7206,13 +7206,13 @@
         </is>
       </c>
       <c r="J18">
-        <v>3.214</v>
+        <v>3.236</v>
       </c>
       <c r="K18">
-        <v>3.926</v>
+        <v>3.918</v>
       </c>
       <c r="L18">
-        <v>2.015</v>
+        <v>2.001</v>
       </c>
       <c r="M18">
         <v>3.512</v>
@@ -7225,27 +7225,27 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>+0.298</t>
+          <t>+0.276</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>+0.013</t>
+          <t>+0.021</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>-0.164</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="S18">
         <v>-0.158</v>
       </c>
       <c r="T18">
-        <v>1.192</v>
+        <v>1.203</v>
       </c>
       <c r="U18">
-        <v>1.205</v>
+        <v>1.191</v>
       </c>
       <c r="V18">
         <v>-0.181</v>
@@ -7263,12 +7263,12 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>+0.207</t>
+          <t>+0.196</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.156</t>
         </is>
       </c>
       <c r="AB18">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:11.183Z</t>
+          <t>2026-05-23T14:00:20.623Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:38.269Z</t>
+          <t>2026-05-23T14:00:47.901Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -7614,13 +7614,13 @@
         </is>
       </c>
       <c r="J20">
-        <v>2.11</v>
+        <v>2.113</v>
       </c>
       <c r="K20">
-        <v>3.554</v>
+        <v>3.549</v>
       </c>
       <c r="L20">
-        <v>3.115</v>
+        <v>3.111</v>
       </c>
       <c r="M20">
         <v>2.141</v>
@@ -7633,27 +7633,27 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>+0.031</t>
+          <t>+0.028</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-0.008</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>-0.168</t>
+          <t>-0.164</t>
         </is>
       </c>
       <c r="S20">
         <v>-0.762</v>
       </c>
       <c r="T20">
-        <v>1.061</v>
+        <v>1.064</v>
       </c>
       <c r="U20">
-        <v>1.29</v>
+        <v>1.287</v>
       </c>
       <c r="V20">
         <v>-0.754</v>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>+0.047</t>
+          <t>+0.044</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.082</t>
+          <t>-0.079</t>
         </is>
       </c>
       <c r="AB20">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:39.391Z</t>
+          <t>2026-05-23T14:00:48.959Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -7821,10 +7821,10 @@
         <v>1.854</v>
       </c>
       <c r="K21">
-        <v>3.707</v>
+        <v>3.713</v>
       </c>
       <c r="L21">
-        <v>3.745</v>
+        <v>3.746</v>
       </c>
       <c r="M21">
         <v>1.865</v>
@@ -7842,22 +7842,22 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-0.112</t>
+          <t>-0.118</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>-0.096</t>
+          <t>-0.097</t>
         </is>
       </c>
       <c r="S21">
         <v>-0.973</v>
       </c>
       <c r="T21">
-        <v>0.979</v>
+        <v>0.977</v>
       </c>
       <c r="U21">
-        <v>1.434</v>
+        <v>1.436</v>
       </c>
       <c r="V21">
         <v>-0.95</v>
@@ -7875,12 +7875,12 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>+0.029</t>
+          <t>+0.031</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.063</t>
+          <t>-0.065</t>
         </is>
       </c>
       <c r="AB21">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:40.502Z</t>
+          <t>2026-05-23T14:00:50.023Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -8025,10 +8025,10 @@
         <v>2.005</v>
       </c>
       <c r="K22">
-        <v>3.6</v>
+        <v>3.598</v>
       </c>
       <c r="L22">
-        <v>3.312</v>
+        <v>3.313</v>
       </c>
       <c r="M22">
         <v>1.897</v>
@@ -8046,19 +8046,19 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>-0.052</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>+0.28</t>
+          <t>+0.279</t>
         </is>
       </c>
       <c r="S22">
         <v>-0.923</v>
       </c>
       <c r="T22">
-        <v>1.122</v>
+        <v>1.123</v>
       </c>
       <c r="U22">
         <v>1.245</v>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.081</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:11.183Z</t>
+          <t>2026-05-23T14:00:54.112Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -8326,17 +8326,17 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1-1:7 / 2-1:7 / 1-0:7.5 / 2-0:8 / 1-2:11</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>胜胜:2.55 / 平胜:4.25 / 平平:5.6 / 负负:7.7 / 平负:9.5</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>中国体彩网竞彩足球计算器</t>
+          <t>中国体彩网竞彩足球计算器+CubeGoal public match filter API https://www.cubegoal.com/odds/84844.html</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -8351,22 +8351,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>主胜-平局</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
@@ -8375,7 +8375,7 @@
         </is>
       </c>
       <c r="AU23">
-        <v>65.26</v>
+        <v>61.06</v>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-05-23T13:26:41.586Z</t>
+          <t>2026-05-23T14:00:51.078Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -8430,10 +8430,10 @@
         </is>
       </c>
       <c r="J24">
-        <v>2.389</v>
+        <v>2.395</v>
       </c>
       <c r="K24">
-        <v>3.895</v>
+        <v>3.897</v>
       </c>
       <c r="L24">
         <v>2.495</v>
@@ -8449,12 +8449,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>-0.079</t>
+          <t>-0.085</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>-0.071</t>
+          <t>-0.073</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -8466,10 +8466,10 @@
         <v>-0.585</v>
       </c>
       <c r="T24">
-        <v>1.122</v>
+        <v>1.124</v>
       </c>
       <c r="U24">
-        <v>1.169</v>
+        <v>1.17</v>
       </c>
       <c r="V24">
         <v>-0.662</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
+          <t>-0.008</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
           <t>-0.006</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>-0.005</t>
         </is>
       </c>
       <c r="AB24">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-05-23T13:24:22.193Z</t>
+          <t>2026-05-23T14:00:52.592Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -8634,13 +8634,13 @@
         </is>
       </c>
       <c r="J25">
-        <v>1.369</v>
+        <v>1.368</v>
       </c>
       <c r="K25">
-        <v>5.615</v>
+        <v>5.611</v>
       </c>
       <c r="L25">
-        <v>6.412</v>
+        <v>6.415</v>
       </c>
       <c r="M25">
         <v>1.356</v>
@@ -8653,50 +8653,50 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>-0.013</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>-0.361</t>
+          <t>-0.357</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>+0.156</t>
+          <t>+0.153</t>
         </is>
       </c>
       <c r="S25">
-        <v>-1.531</v>
+        <v>0.5</v>
       </c>
       <c r="T25">
-        <v>1.906</v>
+        <v>2.02</v>
       </c>
       <c r="U25">
-        <v>1.906</v>
+        <v>1.82</v>
       </c>
       <c r="V25">
-        <v>-1.516</v>
+        <v>0.5</v>
       </c>
       <c r="W25">
-        <v>1.964</v>
+        <v>2.02</v>
       </c>
       <c r="X25">
-        <v>1.879</v>
+        <v>1.82</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>+0.015</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>+0.058</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-0.027</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-05-23T13:25:23.000Z</t>
+          <t>2026-05-23T13:58:54.000Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -8850,13 +8850,13 @@
         </is>
       </c>
       <c r="J26">
-        <v>3.354</v>
+        <v>3.272</v>
       </c>
       <c r="K26">
-        <v>3.562</v>
+        <v>3.534</v>
       </c>
       <c r="L26">
-        <v>2.097</v>
+        <v>2.138</v>
       </c>
       <c r="M26">
         <v>3.709</v>
@@ -8869,17 +8869,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>+0.355</t>
+          <t>+0.437</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>+0.293</t>
+          <t>+0.321</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>-0.214</t>
+          <t>-0.255</t>
         </is>
       </c>
       <c r="S26">
@@ -8892,27 +8892,27 @@
         <v>1.896</v>
       </c>
       <c r="V26">
-        <v>0.313</v>
+        <v>0.281</v>
       </c>
       <c r="W26">
-        <v>1.949</v>
+        <v>1.958</v>
       </c>
       <c r="X26">
-        <v>1.909</v>
+        <v>1.833</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>-0.203</t>
+          <t>-0.235</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>+0.014</t>
+          <t>+0.023</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>+0.013</t>
+          <t>-0.063</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-05-23T13:25:30.000Z</t>
+          <t>2026-05-23T13:59:03.000Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9066,13 +9066,13 @@
         </is>
       </c>
       <c r="J27">
-        <v>1.711</v>
+        <v>1.718</v>
       </c>
       <c r="K27">
-        <v>3.822</v>
+        <v>3.803</v>
       </c>
       <c r="L27">
-        <v>4.747</v>
+        <v>4.727</v>
       </c>
       <c r="M27">
         <v>1.491</v>
@@ -9085,17 +9085,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.227</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>+0.433</t>
+          <t>+0.452</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>+1.354</t>
+          <t>+1.374</t>
         </is>
       </c>
       <c r="S27">
@@ -9111,10 +9111,10 @@
         <v>-0.719</v>
       </c>
       <c r="W27">
-        <v>1.895</v>
+        <v>1.918</v>
       </c>
       <c r="X27">
-        <v>1.951</v>
+        <v>1.929</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -9123,12 +9123,12 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>+0.102</t>
+          <t>+0.125</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>+0.019</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -9227,7 +9227,7 @@
         </is>
       </c>
       <c r="AU27">
-        <v>43.27</v>
+        <v>36.66</v>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-05-23T13:25:31.000Z</t>
+          <t>2026-05-23T13:59:04.000Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-05-23T13:25:31.000Z</t>
+          <t>2026-05-23T14:00:53.683Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -9531,36 +9531,36 @@
         </is>
       </c>
       <c r="S29">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="T29">
-        <v>1.879</v>
+        <v>1.98</v>
       </c>
       <c r="U29">
-        <v>1.795</v>
+        <v>1.88</v>
       </c>
       <c r="V29">
-        <v>-0.047</v>
+        <v>-0.5</v>
       </c>
       <c r="W29">
-        <v>1.821</v>
+        <v>1.98</v>
       </c>
       <c r="X29">
-        <v>1.989</v>
+        <v>1.88</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>+0.203</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>-0.058</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>+0.194</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-05-23T13:25:31.000Z</t>
+          <t>2026-05-23T13:59:04.000Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9714,13 +9714,13 @@
         </is>
       </c>
       <c r="J30">
-        <v>1.812</v>
+        <v>1.813</v>
       </c>
       <c r="K30">
-        <v>3.863</v>
+        <v>3.86</v>
       </c>
       <c r="L30">
-        <v>4.063</v>
+        <v>4.06</v>
       </c>
       <c r="M30">
         <v>1.831</v>
@@ -9733,17 +9733,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>+0.019</t>
+          <t>+0.018</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>-0.121</t>
+          <t>-0.118</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>-0.175</t>
+          <t>-0.172</t>
         </is>
       </c>
       <c r="S30">
@@ -9759,7 +9759,7 @@
         <v>-0.578</v>
       </c>
       <c r="W30">
-        <v>1.888</v>
+        <v>1.887</v>
       </c>
       <c r="X30">
         <v>1.958</v>
@@ -9771,7 +9771,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>-0.003</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="AU30">
-        <v>20.86</v>
+        <v>16.66</v>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-05-23T13:25:31.000Z</t>
+          <t>2026-05-23T13:59:04.000Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -9930,13 +9930,13 @@
         </is>
       </c>
       <c r="J31">
-        <v>2.291</v>
+        <v>2.31</v>
       </c>
       <c r="K31">
-        <v>3.423</v>
+        <v>3.421</v>
       </c>
       <c r="L31">
-        <v>3.066</v>
+        <v>3.036</v>
       </c>
       <c r="M31">
         <v>2.04</v>
@@ -9949,17 +9949,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>-0.251</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>+0.281</t>
+          <t>+0.283</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>+0.219</t>
+          <t>+0.249</t>
         </is>
       </c>
       <c r="S31">
@@ -9975,10 +9975,10 @@
         <v>-0.25</v>
       </c>
       <c r="W31">
-        <v>1.934</v>
+        <v>2.02</v>
       </c>
       <c r="X31">
-        <v>1.862</v>
+        <v>1.846</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -9987,12 +9987,12 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>-0.006</t>
+          <t>+0.08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>-0.055</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-05-23T13:25:14.000Z</t>
+          <t>2026-05-23T13:58:43.000Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="J32">
-        <v>2.195</v>
+        <v>2.192</v>
       </c>
       <c r="K32">
-        <v>3.531</v>
+        <v>3.537</v>
       </c>
       <c r="L32">
-        <v>2.975</v>
+        <v>2.969</v>
       </c>
       <c r="M32">
         <v>2.303</v>
@@ -10165,17 +10165,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>+0.108</t>
+          <t>+0.111</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>-0.142</t>
+          <t>-0.148</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>-0.171</t>
+          <t>-0.165</t>
         </is>
       </c>
       <c r="S32">
@@ -10191,10 +10191,10 @@
         <v>-0.281</v>
       </c>
       <c r="W32">
-        <v>1.964</v>
+        <v>1.952</v>
       </c>
       <c r="X32">
-        <v>1.859</v>
+        <v>1.892</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -10203,12 +10203,12 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>+0.163</t>
+          <t>+0.151</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>-0.085</t>
+          <t>-0.052</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-05-23T13:25:00.000Z</t>
+          <t>2026-05-23T14:00:52.588Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -10395,36 +10395,36 @@
         </is>
       </c>
       <c r="S33">
-        <v>-0.267</v>
+        <v>-0.5</v>
       </c>
       <c r="T33">
-        <v>1.858</v>
+        <v>2.1</v>
       </c>
       <c r="U33">
-        <v>1.957</v>
+        <v>1.7</v>
       </c>
       <c r="V33">
-        <v>-0.483</v>
+        <v>-0.5</v>
       </c>
       <c r="W33">
-        <v>1.999</v>
+        <v>2.1</v>
       </c>
       <c r="X33">
-        <v>1.837</v>
+        <v>1.7</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>-0.216</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>+0.141</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-05-23T13:25:00.000Z</t>
+          <t>2026-05-23T14:00:52.587Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -10611,36 +10611,36 @@
         </is>
       </c>
       <c r="S34">
-        <v>-0.406</v>
+        <v>-0.75</v>
       </c>
       <c r="T34">
-        <v>1.936</v>
+        <v>2.1</v>
       </c>
       <c r="U34">
-        <v>1.872</v>
+        <v>1.7</v>
       </c>
       <c r="V34">
-        <v>-0.5</v>
+        <v>-0.75</v>
       </c>
       <c r="W34">
-        <v>1.904</v>
+        <v>2.1</v>
       </c>
       <c r="X34">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>-0.094</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>-0.032</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-0.012</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-05-23T13:25:07.000Z</t>
+          <t>2026-05-23T13:58:37.000Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -10797,10 +10797,10 @@
         <v>2.076</v>
       </c>
       <c r="K35">
-        <v>3.54</v>
+        <v>3.538</v>
       </c>
       <c r="L35">
-        <v>3.158</v>
+        <v>3.159</v>
       </c>
       <c r="M35">
         <v>1.778</v>
@@ -10818,12 +10818,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>+0.307</t>
+          <t>+0.309</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>+0.732</t>
+          <t>+0.731</t>
         </is>
       </c>
       <c r="S35">
@@ -10839,10 +10839,10 @@
         <v>-0.283</v>
       </c>
       <c r="W35">
-        <v>1.878</v>
+        <v>1.875</v>
       </c>
       <c r="X35">
-        <v>1.94</v>
+        <v>1.948</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -10851,12 +10851,12 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>-0.007</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>+0.017</t>
+          <t>+0.025</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-05-23T13:25:08.000Z</t>
+          <t>2026-05-23T13:58:37.000Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -11010,13 +11010,13 @@
         </is>
       </c>
       <c r="J36">
-        <v>1.881</v>
+        <v>1.852</v>
       </c>
       <c r="K36">
-        <v>3.469</v>
+        <v>3.502</v>
       </c>
       <c r="L36">
-        <v>3.87</v>
+        <v>3.948</v>
       </c>
       <c r="M36">
         <v>1.866</v>
@@ -11029,17 +11029,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-0.015</t>
+          <t>+0.014</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>+0.017</t>
+          <t>-0.016</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>-0.107</t>
+          <t>-0.185</t>
         </is>
       </c>
       <c r="S36">
@@ -11055,10 +11055,10 @@
         <v>-0.517</v>
       </c>
       <c r="W36">
-        <v>1.921</v>
+        <v>1.901</v>
       </c>
       <c r="X36">
-        <v>1.896</v>
+        <v>1.928</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -11067,12 +11067,12 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>-0.026</t>
+          <t>-0.046</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>+0.047</t>
+          <t>+0.079</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-05-23T13:25:08.000Z</t>
+          <t>2026-05-23T13:58:38.000Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -11226,13 +11226,13 @@
         </is>
       </c>
       <c r="J37">
-        <v>1.536</v>
+        <v>1.507</v>
       </c>
       <c r="K37">
-        <v>3.955</v>
+        <v>4.057</v>
       </c>
       <c r="L37">
-        <v>5.74</v>
+        <v>5.934</v>
       </c>
       <c r="M37">
         <v>1.591</v>
@@ -11245,17 +11245,17 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>+0.055</t>
+          <t>+0.084</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>-0.187</t>
+          <t>-0.289</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>-0.677</t>
+          <t>-0.871</t>
         </is>
       </c>
       <c r="S37">
@@ -11271,10 +11271,10 @@
         <v>-0.969</v>
       </c>
       <c r="W37">
-        <v>1.889</v>
+        <v>1.878</v>
       </c>
       <c r="X37">
-        <v>1.871</v>
+        <v>1.884</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>-0.019</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>+0.045</t>
+          <t>+0.058</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-05-23T13:25:08.000Z</t>
+          <t>2026-05-23T13:58:38.000Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -11442,10 +11442,10 @@
         </is>
       </c>
       <c r="J38">
-        <v>2.402</v>
+        <v>2.391</v>
       </c>
       <c r="K38">
-        <v>3.435</v>
+        <v>3.468</v>
       </c>
       <c r="L38">
         <v>2.688</v>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>+0.082</t>
+          <t>+0.093</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>-0.026</t>
+          <t>-0.059</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -11484,27 +11484,27 @@
         <v>1.847</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="W38">
-        <v>1.819</v>
+        <v>1.804</v>
       </c>
       <c r="X38">
-        <v>1.946</v>
+        <v>1.964</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>+0.094</t>
+          <t>+0.11</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>-0.026</t>
+          <t>-0.041</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>+0.099</t>
+          <t>+0.117</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>常规｜资金/赔率支持首选；亚盘变化-0.3</t>
+          <t>常规｜资金/赔率支持首选；亚盘变化-0.32</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>主判断：主胜，防客胜；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.79）；赔率：资金/赔率支持首选（资金/赔率支持首选；亚盘变化-0.3）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，支撑大于风险</t>
+          <t>主判断：主胜，防客胜；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.79）；赔率：资金/赔率支持首选（资金/赔率支持首选；亚盘变化-0.32）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，支撑大于风险</t>
         </is>
       </c>
     </row>
@@ -11934,12 +11934,12 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>常规｜赔率变化平稳；亚盘变化-0.04</t>
+          <t>常规｜赔率变化平稳；亚盘变化-0.03</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>主判断：主胜，防客胜；冷门：中高（概率差过小）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.64）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.04）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防客胜；冷门：中高（概率差过小）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.64）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.03）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -12200,7 +12200,7 @@
         </is>
       </c>
       <c r="L6">
-        <v>48.14</v>
+        <v>46.74</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>中性｜无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.75</t>
+          <t>中性｜无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.77</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>主判断：客胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.75）；赔率：首选热度走弱（首选热度走弱；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
+          <t>主判断：客胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.77）；赔率：首选热度走弱（首选热度走弱；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12300,7 @@
         </is>
       </c>
       <c r="L7">
-        <v>43.27</v>
+        <v>36.66</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -12309,12 +12309,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>低｜主方向概率领先</t>
+          <t>低｜备选赔付不高，市场不排除</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>中性｜无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.74</t>
+          <t>中性｜无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.73</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>主判断：客胜，防主胜；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.74）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
+          <t>主判断：客胜，防主胜；冷门：低（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.73）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>常规｜赔率变化平稳；亚盘变化-0.25</t>
+          <t>常规｜赔率变化平稳；亚盘变化0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.89）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.25）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.89）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -12734,12 +12734,12 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>常规｜赔率变化平稳；亚盘变化-0.25</t>
+          <t>常规｜赔率变化平稳；亚盘变化0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.82）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.25）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.82）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -12900,7 +12900,7 @@
         </is>
       </c>
       <c r="L13">
-        <v>35.91</v>
+        <v>31.71</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -13034,12 +13034,12 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>常规｜赔率变化平稳；亚盘变化-0.14</t>
+          <t>常规｜赔率变化平稳；亚盘变化-0.18</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.92）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.14）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：强信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.92）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化-0.18）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：强信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -13100,7 +13100,7 @@
         </is>
       </c>
       <c r="L15">
-        <v>20.86</v>
+        <v>16.66</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -13296,11 +13296,11 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="L17">
-        <v>30.97</v>
+        <v>26.77</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -13891,16 +13891,16 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="L23">
-        <v>65.26</v>
+        <v>61.06</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -14134,12 +14134,12 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>常规｜赔率变化平稳；亚盘变化+0.02</t>
+          <t>常规｜赔率变化平稳；亚盘变化0</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.95）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化+0.02）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：强信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（主方向概率领先）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.95）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：强信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -14234,12 +14234,12 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>常规｜首选热度走弱；亚盘变化-0.2</t>
+          <t>常规｜首选热度走弱；亚盘变化-0.23</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.79）；赔率：首选热度走弱（首选热度走弱；亚盘变化-0.2）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.79）；赔率：首选热度走弱（首选热度走弱；亚盘变化-0.23）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -14300,7 +14300,7 @@
         </is>
       </c>
       <c r="L27">
-        <v>43.27</v>
+        <v>36.66</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -14534,12 +14534,12 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>常规｜资金/赔率支持首选；亚盘变化+0.2</t>
+          <t>常规｜资金/赔率支持首选；亚盘变化0</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.62）；赔率：资金/赔率支持首选（资金/赔率支持首选；亚盘变化+0.2）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.62）；赔率：资金/赔率支持首选（资金/赔率支持首选；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：中强信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -14600,7 +14600,7 @@
         </is>
       </c>
       <c r="L30">
-        <v>20.86</v>
+        <v>16.66</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -14934,12 +14934,12 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>常规｜首选热度走弱；亚盘变化-0.22</t>
+          <t>常规｜首选热度走弱；亚盘变化0</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>主判断：主胜，防客胜；冷门：低（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.70）；赔率：首选热度走弱（首选热度走弱；亚盘变化-0.22）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防客胜；冷门：低（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.70）；赔率：首选热度走弱（首选热度走弱；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -15034,12 +15034,12 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>常规｜首选热度走弱；亚盘变化-0.09</t>
+          <t>常规｜首选热度走弱；亚盘变化0</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>主判断：主胜，防平局；冷门：低（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.70）；赔率：首选热度走弱（首选热度走弱；亚盘变化-0.09）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防平局；冷门：低（备选赔付不高，市场不排除）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.70）；赔率：首选热度走弱（首选热度走弱；亚盘变化0）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -15434,12 +15434,12 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>常规｜赔率变化平稳；亚盘变化+0.09</t>
+          <t>常规｜赔率变化平稳；亚盘变化+0.11</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>主判断：主胜，防客胜；冷门：中高（概率差过小）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.63）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化+0.09）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
+          <t>主判断：主胜，防客胜；冷门：中高（概率差过小）；大小球：中性（无明确大小球盘口，使用比分/蒙特卡洛推导，模型总进球2.63）；赔率：赔率变化平稳（赔率变化平稳；亚盘变化+0.11）；状态/阵容：近期状态源未完全匹配；未匹配预计/实际阵容，临场需复核；综合：谨慎信心，风险需覆盖</t>
         </is>
       </c>
     </row>
@@ -16400,21 +16400,21 @@
         </is>
       </c>
       <c r="R6">
-        <v>2.747</v>
+        <v>2.766</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -16565,21 +16565,21 @@
         </is>
       </c>
       <c r="R7">
-        <v>2.738</v>
+        <v>2.727</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>防守承压/反击为主</t>
+          <t>均衡偏主动</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -22469,12 +22469,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -22488,35 +22488,35 @@
         </is>
       </c>
       <c r="K6">
-        <v>0.2231</v>
+        <v>0.216</v>
       </c>
       <c r="L6">
-        <v>0.2904</v>
+        <v>0.2838</v>
       </c>
       <c r="M6">
-        <v>0.4866</v>
+        <v>0.5002</v>
       </c>
       <c r="N6">
-        <v>0.2231</v>
+        <v>0.216</v>
       </c>
       <c r="O6">
-        <v>0.2904</v>
+        <v>0.2838</v>
       </c>
       <c r="P6">
-        <v>0.4866</v>
+        <v>0.5002</v>
       </c>
       <c r="Q6">
-        <v>0.1558</v>
+        <v>0.142</v>
       </c>
       <c r="R6">
-        <v>0.214</v>
+        <v>0.2056</v>
       </c>
       <c r="S6">
-        <v>0.6303</v>
+        <v>0.6525</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0-1:12.3% / 0-2:11.9% / 1-2:10.1%</t>
+          <t>0-1:12.4% / 0-2:12.3% / 1-2:9.7%</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -22525,7 +22525,7 @@
         </is>
       </c>
       <c r="V6">
-        <v>48.14</v>
+        <v>46.74</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         </is>
       </c>
       <c r="X6">
-        <v>-0.1144</v>
+        <v>-0.1146</v>
       </c>
       <c r="Y6">
         <v>0</v>
@@ -22597,7 +22597,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -22607,39 +22607,39 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="K7">
-        <v>0.2904</v>
+        <v>0.3001</v>
       </c>
       <c r="L7">
-        <v>0.2531</v>
+        <v>0.2529</v>
       </c>
       <c r="M7">
-        <v>0.4565</v>
+        <v>0.447</v>
       </c>
       <c r="N7">
-        <v>0.2904</v>
+        <v>0.3001</v>
       </c>
       <c r="O7">
-        <v>0.2531</v>
+        <v>0.2529</v>
       </c>
       <c r="P7">
-        <v>0.4565</v>
+        <v>0.447</v>
       </c>
       <c r="Q7">
-        <v>0.2243</v>
+        <v>0.2415</v>
       </c>
       <c r="R7">
-        <v>0.2405</v>
+        <v>0.241</v>
       </c>
       <c r="S7">
-        <v>0.5353</v>
+        <v>0.5176</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1-1:11.5% / 0-1:10.9% / 1-2:10%</t>
+          <t>1-1:11.2% / 0-1:10.8% / 1-2:10%</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -22648,7 +22648,7 @@
         </is>
       </c>
       <c r="V7">
-        <v>43.27</v>
+        <v>36.66</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         </is>
       </c>
       <c r="X7">
-        <v>-0.1144</v>
+        <v>-0.1149</v>
       </c>
       <c r="Y7">
         <v>0</v>
@@ -23386,7 +23386,7 @@
         </is>
       </c>
       <c r="V13">
-        <v>35.91</v>
+        <v>31.71</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -23576,12 +23576,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -23632,7 +23632,7 @@
         </is>
       </c>
       <c r="V15">
-        <v>20.86</v>
+        <v>16.66</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -23832,12 +23832,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>主胜-平局</t>
         </is>
       </c>
       <c r="K17">
@@ -23878,7 +23878,7 @@
         </is>
       </c>
       <c r="V17">
-        <v>30.97</v>
+        <v>26.77</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -24560,22 +24560,22 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>主胜-平局</t>
         </is>
       </c>
       <c r="K23">
@@ -24616,7 +24616,7 @@
         </is>
       </c>
       <c r="V23">
-        <v>65.26</v>
+        <v>61.06</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -25071,13 +25071,13 @@
         </is>
       </c>
       <c r="K27">
-        <v>0.2904</v>
+        <v>0.3001</v>
       </c>
       <c r="L27">
-        <v>0.2531</v>
+        <v>0.2529</v>
       </c>
       <c r="M27">
-        <v>0.4565</v>
+        <v>0.447</v>
       </c>
       <c r="N27">
         <v>0.627</v>
@@ -25108,7 +25108,7 @@
         </is>
       </c>
       <c r="V27">
-        <v>43.27</v>
+        <v>36.66</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         </is>
       </c>
       <c r="V30">
-        <v>20.86</v>
+        <v>16.66</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
